--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4. API Specifications — RT (noetic_bevy runtime)</t>
+          <t>4. API Specifications — RT (noetic runtime)</t>
         </is>
       </c>
       <c r="I1" s="6" t="inlineStr">
@@ -7065,7 +7065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7149,6 +7149,28 @@
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>API-RT-005 think_system moved to noetic_bevy::think (Internal Design 0.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>RT APIs moved from noetic_bevy to noetic (Internal Design 0.3).</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10534,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy runtime: 9 API specifications</t>
+          <t>noetic runtime: 9 API specifications</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10668,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>API-&lt;AREA&gt;-nnn. Areas: APP shell · SIM simulation host · PRJ project/tree/undo · BRN brain graph · WLD world · DBG animal inspector · SPC species · IND individuals · IO files · NET remote debug · COR noetic_core algorithms · RT noetic_bevy runtime.</t>
+          <t>API-&lt;AREA&gt;-nnn. Areas: APP shell · SIM simulation host · PRJ project/tree/undo · BRN brain graph · WLD world · DBG animal inspector · SPC species · IND individuals · IO files · NET remote debug · COR noetic_core algorithms · RT noetic runtime.</t>
         </is>
       </c>
     </row>
@@ -15543,7 +15565,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::plugin</t>
+          <t>noetic::plugin</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -15580,7 +15602,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::asset</t>
+          <t>noetic::asset</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -15617,7 +15639,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::asset</t>
+          <t>noetic::asset</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -15654,7 +15676,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::sync</t>
+          <t>noetic::sync</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -15691,7 +15713,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::think</t>
+          <t>noetic::think</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -15728,7 +15750,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::anim</t>
+          <t>noetic::anim</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -15765,7 +15787,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::debug</t>
+          <t>noetic::debug</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -15802,7 +15824,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::nav</t>
+          <t>noetic::nav</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -560,11 +560,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>詳細設計書</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -586,7 +582,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Detailed Design (詳細設計書)</t>
+          <t>Detailed Design</t>
         </is>
       </c>
     </row>
@@ -598,7 +594,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -658,7 +654,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Basic Design (基本設計書) · External Design (外部設計書, item IDs) · Internal Design (内部設計書, modules and types)</t>
+          <t>Basic Design · External Design (item IDs) · Internal Design (modules and types)</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7171,6 +7167,28 @@
       <c r="D6" s="4" t="inlineStr">
         <is>
           <t>RT APIs moved from noetic_bevy to noetic (Internal Design 0.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Japanese names removed; the documents are in English only.</t>
         </is>
       </c>
     </row>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>fn apply_quick_test(a: &amp;mut Agent, t: QuickTest, w: &amp;mut SimWorld)</t>
+          <t>fn apply_quick_test(w: &amp;mut SimWorld, id: AgentId, t: QuickTest)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>ALG-12: clone each agent into an empty SimWorld with only its shelter/water; place stimulus by distance/side/wind; fixed seed; tick 10 s at 0.1 s; record segments.</t>
+          <t>ALG-12: clone each agent into an empty SimWorld with only its shelter/water; place stimulus by distance/side/wind; fixed seed; tick 10 s in fixed steps of FIXED_DT (PF-08); record segments.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -5182,7 +5182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5211,7 +5211,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>19 APIs</t>
+          <t>23 APIs</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="55" customHeight="1">
+    <row r="5" ht="107" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>API-COR-001</t>
@@ -5290,10 +5290,11 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. Clock.
-2. For agents in id order: PRC-02…15.
-3. World-level marks decay.
-4. Return events.</t>
+          <t>1. Clock (PRC-01).
+2. Agents in id order: think_agent (API-COR-020) where think_due (API-COR-023), with dt = THINK_DT; act_agent (API-COR-021) for all, with dt; the simple mover applies each Movement.
+3. Effects sorted by (source, seq) → apply_effect (API-COR-022); marks stored.
+4. World-level marks decay.
+5. Return events.</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -5372,7 +5373,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>fn perceive(a: &amp;Agent, sp: &amp;Species, w: &amp;WorldView) -&gt; Percepts</t>
+          <t>fn perceive(a: &amp;Agent, sp: &amp;Species, view: &amp;dyn WorldView) -&gt; Percepts</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -5466,7 +5467,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>fn update_fear(a: &amp;mut Agent, p: &amp;Percepts, w: &amp;WorldView, dt: f32)</t>
+          <t>fn update_fear(a: &amp;mut Agent, p: &amp;Percepts, view: &amp;dyn WorldView, dt: f32)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -5513,7 +5514,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>fn threat_branch(a: &amp;mut Agent, brain: &amp;Brain, rng: &amp;mut Rng) -&gt; Option&lt;SimEvent&gt;</t>
+          <t>fn threat_branch(a: &amp;mut Agent, sp: &amp;Species, out: &amp;mut Outbox)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -5528,7 +5529,8 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>ALG-06.</t>
+          <t>ALG-06 with a.rng.
+Anim and Reacted go to out.events.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -5594,7 +5596,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="29" customHeight="1">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>API-COR-008</t>
@@ -5607,7 +5609,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>fn propagate_alarm(w: &amp;mut SimWorld, src: AgentId, kind: AlarmKind)</t>
+          <t>fn propagate_alarm(b: &amp;mut Agent, kind: AlarmKind, src: AgentId, dist: f32, same_species: bool)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -5622,7 +5624,8 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>ALG-08.</t>
+          <t>ALG-08 for one receiver.
+Called by apply_effect for each agent in the alarm radius.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -5654,7 +5657,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>fn choose_activity(a: &amp;Agent, sp: &amp;Species, acts: &amp;Activities, hour: f32, rng: &amp;mut Rng) -&gt; (ActivityId, Scores)</t>
+          <t>fn choose_activity(a: &amp;mut Agent, sp: &amp;Species, acts: &amp;Activities, hour: f32, out: &amp;mut Outbox) -&gt; (ActivityId, Scores)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -5669,7 +5672,8 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>ALG-10.</t>
+          <t>ALG-10 with a.rng; hour = view.hour().
+Chose goes to out.events.</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -5716,7 +5720,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>ALG-10a.</t>
+          <t>ALG-10 (curve).</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -5748,7 +5752,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>fn run_step(a: &amp;mut Agent, step: &amp;Step, w: &amp;mut SimWorld, dt: f32) -&gt; StepStatus</t>
+          <t>fn run_step(a: &amp;mut Agent, step: &amp;Step, view: &amp;dyn WorldView, dt: f32, out: &amp;mut Outbox) -&gt; StepStatus</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -5763,8 +5767,8 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1. On start: duration = rng.range(min,max); emit AnimEvent.
-2. Move steps: path to target (memory or perception); fail if none → choose again.
+          <t>1. On start: duration = a.rng.range(min,max); SimEvent::Anim to out.events.
+2. Move steps: target from memory or perception; fail if none or on MoveFailed → choose again.
 3. Act steps: lower need while running.
 4. Done when time over or target reached.</t>
         </is>
@@ -5798,7 +5802,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>fn follow_group(a: &amp;mut Agent, w: &amp;WorldView)</t>
+          <t>fn follow_group(a: &amp;mut Agent, view: &amp;dyn WorldView)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -5814,7 +5818,7 @@
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. If leader alive: target = leader.pos + offset(id).
-2. Leader dead → elect oldest member.</t>
+2. Leader dead → the living member with the lowest AgentId leads; each member works it out from the view, none writes another.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -5833,7 +5837,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="29" customHeight="1">
+    <row r="17" ht="55" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>API-COR-013</t>
@@ -5846,7 +5850,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>fn fight(a: AgentId, b: AgentId, w: &amp;mut SimWorld, rng: &amp;mut Rng)</t>
+          <t>fn fight(a: &amp;mut Agent, view: &amp;dyn WorldView, dt: f32, out: &amp;mut Outbox)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -5861,7 +5865,8 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>ALG-11.</t>
+          <t>ALG-11 for one side.
+Damage and the challenge go to out; the rival answers in its own think.</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -5893,7 +5898,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>fn apply_damage(a: &amp;mut Agent, sp: &amp;Species, dmg: f32) / fn heal(a: &amp;mut Agent, sp: &amp;Species, dt_h: f32)</t>
+          <t>fn apply_damage(a: &amp;mut Agent, sp: &amp;Species, dmg: f32, out: &amp;mut Outbox) / fn heal(a: &amp;mut Agent, sp: &amp;Species, dt_h: f32)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -5940,7 +5945,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>fn leave_mark(...) / fn decay_marks(w: &amp;mut SimWorld, dt_h: f32)</t>
+          <t>fn leave_mark(a: &amp;mut Agent, sp: &amp;Species, out: &amp;mut Outbox) / fn decay_marks(marks: &amp;mut Vec&lt;ScentMark&gt;, dt_h: f32)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -5955,7 +5960,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>1. Leave when urge to mark ≥ threshold and interval passed.
+          <t>1. Leave when urge to mark ≥ threshold and interval passed: Effect::Mark in out.
 2. strength = 1 − age/lifetime; remove at 0.</t>
         </is>
       </c>
@@ -5975,7 +5980,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="29" customHeight="1">
+    <row r="20" ht="55" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>API-COR-016</t>
@@ -5988,7 +5993,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>fn locomotion(a: &amp;mut Agent, sp: &amp;Species, w: &amp;WorldView, dt: f32)</t>
+          <t>fn locomotion(a: &amp;mut Agent, sp: &amp;Species, dt: f32) -&gt; Movement</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -5998,12 +6003,13 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Movement</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>ALG-13.</t>
+          <t>1. ALG-13: target, gait, speed and gaze; never writes a.pos.
+2. SimWorld (editor) applies it in sim::tick with the simple mover; in the game the game moves the body.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -6162,6 +6168,203 @@
       <c r="I23" s="4" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="107" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>API-COR-020</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>think_agent</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>pub fn think_agent(a: &amp;mut Agent, sp: &amp;Species, view: &amp;dyn WorldView, dt: f32, out: &amp;mut Outbox)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>dt = THINK_DT (s)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1. Skip if Dead (PRC-02).
+2. In this order: heal, update_needs, perceive, update_memory, update_fear, threat_branch, choose_activity (PRC-03…10).
+3. dt_h = dt / secs_per_game_hour for the per-hour rates.
+4. Writes only a; effects for other agents and SimEvents go to out.</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>think_system (API-RT-005), tick (API-COR-001)</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Same agent, view and dt give the same agent and effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="68" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>API-COR-021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>act_agent</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>pub fn act_agent(a: &amp;mut Agent, sp: &amp;Species, view: &amp;dyn WorldView, dt: f32, out: &amp;mut Outbox) -&gt; Movement</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>dt = fixed_dt (s)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1. Skip if Dead.
+2. In this order: run_step, follow_group, fight, leave_mark, locomotion (PRC-11…15).
+3. Writes only a; damage, challenges and marks go to out.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>act_system (API-RT-010), tick (API-COR-001)</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="81" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>API-COR-022</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>apply_effect</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>pub fn apply_effect(e: &amp;Effect, b: &amp;mut Agent, sp: &amp;Species, dist: f32, out: &amp;mut Outbox)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1. Alarm → propagate_alarm (ALG-08).
+2. Damage → apply_damage (ALG-11b).
+3. Challenge → remember the rival; its next think fights back or flees (ALG-11).
+4. The host picks the receivers in id order and stores Mark itself.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>apply_effects_system (API-RT-011), tick (API-COR-001)</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Effects produced in any order give the same result once sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="55" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>API-COR-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>think_due</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>pub fn think_due(id: AgentId, step: u64, stride: u32) -&gt; bool</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>stride = max(1, round(fixed_hz / think_hz))</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1. (step + id) % stride == 0.
+2. Every agent thinks once every stride steps, and the agents spread evenly over the steps.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>think_system (API-RT-005), tick (API-COR-001)</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Each agent due exactly once per stride steps</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6210,7 +6413,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>9 APIs</t>
+          <t>11 APIs</t>
         </is>
       </c>
     </row>
@@ -6290,8 +6493,8 @@
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. init_asset::&lt;NoeticSpecies&gt;() + loader.
-2. Systems in NoeticSet::{Sync, Think, Act, Events} in FixedUpdate.
-3. Event NoeticAnimEvent.
+2. Systems in NoeticSet::{Sync, Think, Act, Apply, Events} in FixedUpdate.
+3. Events NoeticAnimEvent, NoeticAlarm, NoeticDied.
 4. If feature "debug": RemotePlugin methods (API-RT-007).</t>
         </is>
       </c>
@@ -6406,7 +6609,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="94" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>API-RT-004</t>
@@ -6435,7 +6638,10 @@
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Spatial grid (cell 8 m) of world features and agents.
-2. Player/noise stimuli.</t>
+2. Player/noise stimuli.
+3. Marker zones (Cover, Mud…) answer terrain_at; unmarked ground is open.
+4. Agent positions read back from Transform: the game moved them.
+5. New NoeticAgent: AgentId from a counter (same-step spawns sorted by Entity), added to AgentOrder; despawned agents removed.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -6454,7 +6660,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="29" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>API-RT-005</t>
@@ -6482,8 +6688,8 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. Round-robin agents per frame at think_hz (default 10).
-2. Call core stages PRC-03…14.</t>
+          <t>1. Walk AgentOrder; agents with think_due (API-COR-023) run think_agent (API-COR-020) with dt = THINK_DT.
+2. May run in parallel (PF-04): each agent writes only itself and its own Effect buffer.</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -6530,7 +6736,9 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1. Map SimEvent::Anim to NoeticAnimEvent{entity, event, clip, looping}.</t>
+          <t>1. Drain the SimEvents of every agent Outbox in AgentOrder.
+2. Anim → NoeticAnimEvent{entity, event, clip, looping}; clip = the species animation_clips entry for the event, if any.
+3. Died → NoeticDied.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -6597,7 +6805,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="94" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>API-RT-008</t>
@@ -6605,12 +6813,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>NoeticNavigator</t>
+          <t>MoveIntent</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>pub trait NoeticNavigator: Send + Sync { fn path(&amp;self, from: Vec3, to: Vec3) -&gt; Option&lt;Path&gt;; }</t>
+          <t>#[derive(Component)] pub struct MoveIntent(pub Movement); #[derive(Component)] pub struct MoveFailed;</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -6625,7 +6833,9 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1. Default: straight line with obstacle avoidance.</t>
+          <t>1. act_system writes it on every agent each fixed step.
+2. The game moves the Transform toward the target with its own navigation; sync_world_system reads the position back and GoTo ends near the target.
+3. Optional: the game inserts MoveFailed when the target is unreachable; the step fails and Noetic removes the marker. Without it the step ends at its max duration.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -6689,6 +6899,104 @@
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-010</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>act_system</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>fn act_system(order: Res&lt;AgentOrder&gt;, q: Query&lt;(&amp;mut AgentBrainState, &amp;mut MoveIntent, Option&lt;&amp;MoveFailed&gt;)&gt;, ...)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. Walk AgentOrder; act_agent (API-COR-021) with dt = fixed_dt.
+2. Movement → MoveIntent; MoveFailed fails the step and is removed.</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="94" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-011</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>apply_effects_system</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>fn apply_effects_system(order: Res&lt;AgentOrder&gt;, view: Res&lt;WorldViewCache&gt;, ...)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. Merge every agent Effect buffer; sort by (source id, seq).
+2. Receivers in id order: alarm → agents in its radius (WorldViewCache); damage and challenge → their target; apply_effect (API-COR-022).
+3. Mark → spawn a ScentMark entity; decay despawns it at strength 0.
+4. Alarm → NoeticAlarm for the game.</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Same effects in another production order give the same agents</t>
         </is>
       </c>
     </row>
@@ -6818,7 +7126,7 @@
         <is>
           <t>let gain  = percepts.best * (0.4 + a.traits.fear as f32 / 100.0 * 1.2) * 60.0 * dt;   // from prototype
 let mut decay = 8.0 * (0.5 + (100.0 - a.traits.fear as f32) / 100.0);
-if world.own_safe_mark_within(a, 6.0) { decay *= 1.5; }
+if view.marks_near(a.pos, 6.0).iter().any(|m| m.species == a.species &amp;&amp; m.meaning == Meaning::Safe) { decay *= 1.5; }
 a.fear = (a.fear + gain - decay * dt).clamp(0.0, 100.0);
 // pain (ALG-11b) adds: dmg * (1 - pain_resist) * 2</t>
         </is>
@@ -6898,10 +7206,11 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="79" customHeight="1">
+    <row r="26" ht="92" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <t>// radius and reach: Thump 15 m (same species ×1, others ×0.5) · TailFlag 40 m (own group) · Chirp 35 m (all species)
+// run by apply_effect (API-COR-022) for each queued Effect::Alarm, receivers in id order
 for b in world.neighbours(src.pos, radius) {
     let k = (1.0 - dist / radius) * reach(kind, b.species == src.species) * (0.5 + b.traits.fear as f32 / 100.0);
     b.fear = (b.fear + 60.0 * k).min(100.0);
@@ -6960,10 +7269,11 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="54" customHeight="1">
+    <row r="35" ht="67" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>// urge to fight rises +aggro/100 × 6 per game hour; ≥ 70 and same-species rival ≤ 12 m → GoToRival → Scuffle
+          <t>// a and the rival each run fight() in their own act; damage and the challenge cross over as Effects (API-COR-022)
+// urge to fight rises +aggro/100 × 6 per game hour; ≥ 70 and same-species rival ≤ 12 m → GoToRival → Scuffle
 // each scuffle round (1.5–3 s): dmg = (2.0 + aggro/20) × rng.range(0.7, 1.3) to the other
 // opponent: fights back if stubborn + aggro &gt; 90 + rng.below(40), otherwise flees (Reacting: Flee)
 // loser = lower health ratio at the end; winner's urge resets to 0; failed approach → cooldown 60 s</t>
@@ -6983,7 +7293,7 @@
           <t>a.health -= dmg;
 a.fear = (a.fear + dmg * (1.0 - sp.health.pain_resist) * 2.0).min(100.0);
 a.limping = a.health / sp.health.max &lt; sp.health.limp_below;      // speed × 0.6
-if a.health &lt;= 0.0 { a.state = Dead; emit(Died) }
+if a.health &lt;= 0.0 { a.state = Dead; out.events.push(SimEvent::Died { agent: a.id }) }
 // heal per game hour: heal_per_h × (2.0 if resting else 1.0), up to max</t>
         </is>
       </c>
@@ -7004,7 +7314,7 @@
     let mut a = src.agent(id).clone(); a.state = Choosing; a.fear = 0.0; a.rng = Rng::seed(a.seed ^ 0x5EED);
     let pos = a.pos + dir(side, a.heading) * stimulus.dist; w.add_stimulus(stimulus.at(pos, wind));
     w.agents.push(a);
-    for _ in 0..(secs / 0.1) as usize { tick(&amp;mut w, 0.1); record_segment(&amp;w, id, &amp;mut segs); }
+    for _ in 0..(secs / FIXED_DT) as usize { tick(&amp;mut w, FIXED_DT); record_segment(&amp;w, id, &amp;mut segs); }
     results.push(SandboxResult { id, segs, reacted: segs.iter().any(|s| s.is_reaction) });
 }
 // the source world is never borrowed mutably</t>
@@ -7018,14 +7328,17 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="66.5" customHeight="1">
+    <row r="44" ht="106.5" customHeight="1">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>let base = if fleeing { sp.locomotion.flee_speed } else { sp.locomotion.speed };
+          <t>// intent: Noetic decides where and how; it never writes a.pos (the game, or the editor mover, moves the body)
+let base = if fleeing { sp.locomotion.flee_speed } else { sp.locomotion.speed };
+let speed = base * if a.limping { 0.6 } else { 1.0 };
+// Zigzag (flee) → the target shifts ± 35° sideways every rng.range(0.6, 1.0) s, so the mover only follows it
+Movement { target: step target, gait: from the step and species (hop, walk, trot, run, zigzag, fly…), speed, gaze: strongest percept }
+// simple mover, editor SimWorld only (sim::tick):
 let terrain = match world.terrain_at(a.pos) { River =&gt; 0.5, Hill =&gt; 0.75, Mud =&gt; 0.8, _ =&gt; 1.0 };   // birds: 1.0
-let speed = base * terrain * if a.limping { 0.6 } else { 1.0 };
-// gaits: Hop → move 0.35 s / pause 0.25 s · Zigzag (flee) → heading ± 35° every rng.range(0.6, 1.0) s
-// Bird → fly straight, land on Tree when Perch step; ponds block ground animals (steer around)</t>
+// Hop → move 0.35 s / pause 0.25 s · Bird → fly straight, land on Tree when Perch step; ponds block ground animals (steer around)</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7189,6 +7502,72 @@
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Japanese names removed; the documents are in English only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>The game moves the animals: API-RT-008 NoeticNavigator replaced by the MoveIntent component; API-COR-016 returns a Movement and never moves the agent; API-RT-004 reads positions back and answers terrain_at from marker zones; ALG-13 split into the intent and the editor simple mover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>One agent pipeline: new API-COR-020 think_agent, COR-021 act_agent, COR-022 apply_effect, COR-023 think_due, API-RT-010 act_system, RT-011 apply_effects_system. Core functions take &amp;dyn WorldView and an Effects queue instead of &amp;mut SimWorld (COR-001, 008, 011, 013, 015; RT-004, RT-005; ALG-08, ALG-11). UT-036…038.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Coherence review: per-agent functions write an Outbox (TYP-24) for effects and SimEvents; threat_branch and choose_activity use a.rng (COR-006, 009, 011, 013…015, 020…022); perceive, update_fear and follow_group take &amp;dyn WorldView; the group leader is derived, never elected; ALG-05 uses view.marks_near; sandbox ticks fixed_dt (ALG-12, IND-008); quick_test takes the world and an id; SIM-005 secs_per_game_hour; RT-001 registers Apply and all three events; RT-006 drains the Outbox; English UI leftovers.</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10282,6 +10661,105 @@
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>UT-036</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>API-COR-023</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>think_due</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>stride 6, ids 0…11, steps 0…5</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>every id due exactly once</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="29" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>UT-037</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>API-COR-022</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>apply_effect</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>two thumps from agents 3 and 7 queued in either order</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>same fear in every receiver once sorted</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>UT-038</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>API-COR-020</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>think_agent</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>same agent, view, dt and seed twice</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>identical agent and effects</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10537,7 +11015,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>noetic_core algorithms: 19 API specifications</t>
+          <t>noetic_core algorithms: 23 API specifications</t>
         </is>
       </c>
     </row>
@@ -10552,7 +11030,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>noetic runtime: 9 API specifications</t>
+          <t>noetic runtime: 11 API specifications</t>
         </is>
       </c>
     </row>
@@ -10612,7 +11090,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>35 unit test cases (normal, boundary, abnormal)</t>
+          <t>38 unit test cases (normal, boundary, abnormal)</t>
         </is>
       </c>
     </row>
@@ -10774,7 +11252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10801,7 +11279,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>137 APIs</t>
+          <t>143 APIs</t>
         </is>
       </c>
     </row>
@@ -12748,7 +13226,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Toolbar status: ✓ or "N soltos" chip.</t>
+          <t>Toolbar status: ✓ or "N loose" chip.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -13039,7 +13517,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Command</t>
+          <t>fn</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -14867,7 +15345,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="16" customHeight="1">
+    <row r="114" ht="29" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
           <t>API-COR-001</t>
@@ -14890,12 +15368,12 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>One simulation step (PRC-01…16).</t>
+          <t>One SimWorld step for the editor: think_agent, act_agent and apply_effect in PRC order.</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>PRC-01…16</t>
+          <t>PRC-01…17</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -15126,7 +15604,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
+    <row r="121" ht="29" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>API-COR-008</t>
@@ -15149,7 +15627,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Alarm raises fear of neighbours (any species).</t>
+          <t>Raises the fear of one neighbour for a queued alarm (any species).</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -15422,7 +15900,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="16" customHeight="1">
+    <row r="129" ht="29" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
           <t>API-COR-016</t>
@@ -15445,7 +15923,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Move with gait and terrain.</t>
+          <t>Movement intent (target, gait, speed, gaze); never moves the agent.</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -15573,32 +16051,32 @@
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>API-RT-001</t>
+          <t>API-COR-020</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>NoeticPlugin::build</t>
+          <t>think_agent</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>noetic::plugin</t>
+          <t>noetic_core::sim</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Plugin</t>
+          <t>fn</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Register assets, components, systems, events.</t>
+          <t>Think stages for one agent (PRC-03…10).</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>FR-603</t>
+          <t>NFR-02, NFR-03</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -15607,35 +16085,35 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="16" customHeight="1">
+    <row r="134" ht="29" customHeight="1">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>API-RT-002</t>
+          <t>API-COR-021</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>SpeciesLoader</t>
+          <t>act_agent</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>noetic::asset</t>
+          <t>noetic_core::sim</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>AssetLoader</t>
+          <t>fn</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Load FMT-01 as asset.</t>
+          <t>Act stages for one agent (PRC-11…15); returns its Movement.</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>FR-603</t>
+          <t>NFR-02</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -15647,143 +16125,143 @@
     <row r="135" ht="16" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>API-RT-003</t>
+          <t>API-COR-022</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>hot_reload_system</t>
+          <t>apply_effect</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
+          <t>noetic_core::sim</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>Apply one queued Effect to one agent (PRC-17).</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>FR-504, FR-507</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>API-COR-023</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>think_due</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::sim</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>fn (pure)</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Whether an agent thinks on this fixed step.</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>NFR-04</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-001</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>NoeticPlugin::build</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>noetic::plugin</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Plugin</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Register assets, components, systems, events.</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>FR-603</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-002</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>SpeciesLoader</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
           <t>noetic::asset</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Swap brain on asset change.</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>PRC-23</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="29" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>API-RT-004</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>sync_world_system</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>noetic::sync</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>System (NoeticSet::Sync)</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>Read game components into the core world view.</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>FR-604</t>
-        </is>
-      </c>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="29" customHeight="1">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>API-RT-005</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>think_system</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>noetic::think</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>System (NoeticSet::Think)</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>Run core decision per agent at configured rate.</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>NFR-04</t>
-        </is>
-      </c>
-      <c r="G137" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="29" customHeight="1">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>API-RT-006</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>anim_event_system</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>noetic::anim</t>
-        </is>
-      </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>System (NoeticSet::Events)</t>
+          <t>AssetLoader</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Emit animation events for the game.</t>
+          <t>Load FMT-01 as asset.</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>IF-03</t>
+          <t>FR-603</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -15795,109 +16273,331 @@
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
+          <t>API-RT-003</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>hot_reload_system</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>noetic::asset</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Swap brain on asset change.</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>PRC-23</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="29" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-004</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>sync_world_system</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>noetic::sync</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>System (NoeticSet::Sync)</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Read game components into the core world view.</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>FR-604</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="29" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-005</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>think_system</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>noetic::think</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>System (NoeticSet::Think)</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Run think_agent for the agents due this step.</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>NFR-04</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="29" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-006</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>anim_event_system</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>noetic::anim</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>System (NoeticSet::Events)</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Emit animation events for the game.</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>IF-03</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
           <t>API-RT-007</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>brp_methods</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>noetic::debug</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr">
         <is>
           <t>BRP handlers</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="E143" s="4" t="inlineStr">
         <is>
           <t>Remote debug read-only methods (feature debug).</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="F143" s="4" t="inlineStr">
         <is>
           <t>IF-02, SEC-01</t>
         </is>
       </c>
-      <c r="G139" s="4" t="inlineStr">
+      <c r="G143" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+    <row r="144" ht="29" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>API-RT-008</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>NoeticNavigator</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>MoveIntent</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>noetic::nav</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>Trait</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>Navigation adapter for navmesh crates.</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Movement intent the game reads to move the animal; MoveFailed comes back.</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>IF-05</t>
         </is>
       </c>
-      <c r="G140" s="4" t="inlineStr">
+      <c r="G144" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>API-RT-009</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>extension_registry</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>noetic_core::ext</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>Resource</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
         <is>
           <t>Register custom nodes from Rust.</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="F145" s="4" t="inlineStr">
         <is>
           <t>FR-606</t>
         </is>
       </c>
-      <c r="G141" s="4" t="inlineStr">
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="29" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-010</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>act_system</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>noetic::think</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>System (NoeticSet::Act)</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Run act_agent for every agent; write MoveIntent.</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>FR-509</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="29" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>API-RT-011</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>apply_effects_system</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>noetic::think</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>System (NoeticSet::Apply)</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Apply every queued Effect in order.</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>FR-504, FR-507</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
@@ -20154,7 +20854,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Shows the planned path.</t>
+          <t>Shows a line to the current movement target.</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -23679,7 +24379,7 @@
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Load embedded logo image.
-2. Text "noetic · Fauna viva".</t>
+2. Text "noetic · Living fauna".</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -24015,7 +24715,7 @@
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Validate ∈ {5,10,20,40}.
-2. clock.hours_per_sec = 24 / (real_minutes × 60).</t>
+2. clock.secs_per_game_hour = real_minutes × 60 / 24.</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -24254,7 +24954,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. Name "Nova pasta" + unique suffix.
+          <t>1. Name "New folder" + unique suffix.
 2. Push to tree; push Undo(CreateFolder).
 3. Start inline rename.</t>
         </is>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t xml:space="preserve">0.11</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>25 APIs</t>
+          <t xml:space="preserve">26 APIs</t>
         </is>
       </c>
     </row>
@@ -877,14 +877,14 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. API-BRN-005 rules.
+          <t xml:space="preserve">1. API-BRN-005 rules.
 2. Add edge; if source is Threat/Reaction with ≥1 edge, split weights equally (sum 100) and toast MSG-008.
-3. Recompile species (API-BRN-002); Undo.</t>
+3. The EditorCommand wrapper recompiles the species into the Project (API-BRN-002); Undo.</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>ConnectError → MSG-001/002/003</t>
+          <t xml:space="preserve">Cycle, SelfLoop → MSG-001; Kind → MSG-023; Duplicate → MSG-024</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -926,9 +926,9 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. Remove edge.
+          <t xml:space="preserve">1. Remove edge.
 2. Re-normalize sibling weights to 100.
-3. Recompile; Undo.</t>
+3. The command wrapper recompiles (API-BRN-002); Undo.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Kind|Cycle|Duplicate</t>
+          <t xml:space="preserve">Kind|Cycle|Duplicate|SelfLoop</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>See ALG-07: keep edited value, distribute the remainder over the other edges proportionally to their old values (equal split if all 0); integer rounding with largest-remainder.</t>
+          <t xml:space="preserve">See ALG-07: keep edited value, distribute the remainder over the other edges proportionally to their old values (equal split if all 0); integer rounding with largest-remainder; toast MSG-008.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1168,9 +1168,9 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. Fixed nodes → MSG-004.
+          <t xml:space="preserve">1. Fixed nodes → MSG-004.
 2. Remove node + edges; for steps reconnect neighbours.
-3. Recompile; toast with Undo.</t>
+3. The command wrapper recompiles (API-BRN-002); toast MSG-009 with Undo.</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1217,8 +1217,8 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1. Replace node.reaction keeping edges.
-2. Recompile.</t>
+          <t xml:space="preserve">1. Replace node.reaction keeping edges.
+2. The command wrapper recompiles (API-BRN-002).</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>fn set_fear_threshold(sp: &amp;mut Species, v: u8)</t>
+          <t xml:space="preserve">fn set_fear_threshold(sp: &amp;mut Species, v: f32)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>fn update_activity(a: &amp;mut Activity, patch: ActivityPatch)</t>
+          <t xml:space="preserve">fn update_activity(p: &amp;mut Project, act: ActivityId, patch: ActivityPatch) -&gt; Result&lt;(), NameError&gt;</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>NameError</t>
+          <t xml:space="preserve">NameError → MSG-029</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>SCR-02-08, SCR-03-09, SCR-03-12, SCR-03-13, SCR-03-15</t>
+          <t xml:space="preserve">SCR-03-09, SCR-03-12, SCR-03-13, SCR-03-15</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>1. Compile steps (API-BRN-016).
+          <t xml:space="preserve">1. The command wrapper compiles the steps into the activity (API-BRN-016).
 2. Pop breadcrumb.</t>
         </is>
       </c>
@@ -1554,9 +1554,9 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>1. Validate 0.1 ≤ min ≤ max ≤ 120.
+          <t xml:space="preserve">1. Validate 0.1 ≤ min ≤ max ≤ 120.
 2. anim: snake_case or empty.
-3. Apply; recompile.</t>
+3. Apply; the command wrapper recompiles (API-BRN-002).</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>fn follow_agent(view: &amp;mut GraphView, agent: Option&lt;AgentId&gt;)</t>
+          <t xml:space="preserve">fn follow_agent(view: &amp;mut GraphView, sim: &amp;mut SimHost, agent: Option&lt;AgentId&gt;)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1603,8 +1603,8 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>1. Set followed agent.
-2. If none exists and requested: spawn one (API-WLD-005) and toast MSG-019.</t>
+          <t xml:space="preserve">1. Set followed agent.
+2. If none exists and requested: spawn one of the current species near its shelter, seeded from the SimHost Rng (API-WLD-005) and toast MSG-019.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1844,7 +1844,8 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>1. loose = API-BRN-006.len().</t>
+          <t xml:space="preserve">1. The caller passes loose = API-BRN-006.len().
+2. loose &gt; 0 → MSG-007 chip in the graph toolbar.</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -1955,6 +1956,55 @@
       <c r="I29" s="4" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="55" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-BRN-026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_activity</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fn create_activity(p: &amp;mut Project, folder: Option&lt;FolderId&gt;) -&gt; ActivityId</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">folder</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ActivityId</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Name "New activity", then "New activity (2)"… until unique (UI-07).
+2. need Hunger, curve Linear, weight 1.0, no steps.
+3. Add to the library in folder; select it and start the inline rename, committed with API-PRJ-002; Undo(Create).</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCR-02-08</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The new name never clashes</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2276,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. Player: move/create NoeticPlayer (state still/walking; cover from terrain).
+          <t xml:space="preserve">1. Player: move/create the player stimulus in w.stimuli (state still/walking; cover from terrain); in a game NoeticPlayer plays this part.
 2. Noise: transient Stimulus{radius:40m, ttl:1s}.
 3. Food: Food item.</t>
         </is>
@@ -2260,7 +2310,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>fn spawn_agent(w: &amp;mut SimWorld, sp: SpeciesId, pos: Vec2, seed: u64) -&gt; AgentId</t>
+          <t xml:space="preserve">fn spawn_agent(w: &amp;mut SimWorld, sp: SpeciesId, pos: Vec2, seed: u64) -&gt; Option&lt;AgentId&gt;</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -2270,14 +2320,14 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>AgentId</t>
+          <t xml:space="preserve">Option&lt;AgentId&gt;</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. Personality = API-IND-001(seed).
+          <t xml:space="preserve">1. Unknown species → None; (traits, quirks) = API-IND-001(species, seed).
 2. Name from species name pool; needs randomized 10–40; health = max.
-3. Group leader assignment for group species.</t>
+3. Group species: join the nearest group of its species; the leader is derived from the view, never stored (API-COR-012).</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -2691,7 +2741,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>fn select_agent(sel: &amp;mut Selection, id: Option&lt;AgentId&gt;)</t>
+          <t xml:space="preserve">fn select_agent(sel: &amp;mut Selection, w: &amp;SimWorld, pick: Pick)   // enum Pick { At(Vec2), Agent(AgentId) }</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2706,7 +2756,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>1. Hit test within 1.5 m; nearest wins.
+          <t xml:space="preserve">1. Pick::At (map click): hit test within 1.5 m, nearest wins, nothing there clears the selection; Pick::Agent (list row): that agent.
 2. Selection=Agent; camera follow optional.</t>
         </is>
       </c>
@@ -3075,7 +3125,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>fn apply_quick_test(w: &amp;mut SimWorld, id: AgentId, t: QuickTest)</t>
+          <t xml:space="preserve">fn quick_test(w: &amp;mut SimWorld, id: AgentId, t: QuickTest)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3127,7 +3177,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>fn locate_agent(cam: &amp;mut WorldCam, id: AgentId)</t>
+          <t xml:space="preserve">fn locate_agent(cam: &amp;mut WorldCam, area: &amp;mut NextState&lt;Area&gt;, w: &amp;SimWorld, id: AgentId)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -3340,7 +3390,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>FieldError::Range → clamped</t>
+          <t xml:space="preserve">Out of range → clamped, no error; unknown field → FieldError</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -3367,7 +3417,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>fn create_species(p: &amp;mut Project, req: NewSpecies) -&gt; Result&lt;SpeciesId, NameError&gt;</t>
+          <t xml:space="preserve">fn create_species(p: &amp;mut Project, sim: &amp;mut SimHost, req: NewSpecies) -&gt; Result&lt;SpeciesId, NameError&gt;</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3390,7 +3440,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>NameError</t>
+          <t xml:space="preserve">NameError → MSG-029</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -3580,7 +3630,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>MSG-015</t>
+          <t xml:space="preserve">Empty name → MSG-015; duplicate → MSG-029</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -3622,7 +3672,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1. Remove; toast + Undo.</t>
+          <t xml:space="preserve">1. Remove; MSG-016 with Undo.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -3669,8 +3719,8 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1. For each unlocked agent: new seed; API-IND-001.
-2. Toast with count.</t>
+          <t xml:space="preserve">1. For each unlocked agent: new seed; API-IND-001.
+2. MSG-030 with the count.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -3844,7 +3894,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>fn set_species_tab(v: &amp;mut SpeciesView, tab: SpeciesTab)</t>
+          <t xml:space="preserve">fn species_tab(v: &amp;mut SpeciesView, tab: SpeciesTab)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3987,12 +4037,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>fn generate_personality(base: &amp;PersonalityBase, seed: u64) -&gt; TraitMap</t>
+          <t xml:space="preserve">fn generate_personality(sp: &amp;Species, seed: u64) -&gt; (TraitMap, Vec&lt;String&gt;)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>base, seed</t>
+          <t xml:space="preserve">species, seed</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4034,7 +4084,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>fn reroll_agent(a: &amp;mut Agent, rng: &amp;mut Rng)</t>
+          <t xml:space="preserve">fn reroll_agent(a: &amp;mut Agent, sp: &amp;Species, rng: &amp;mut Rng)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4049,8 +4099,8 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. Refuse if locked.
-2. seed = rng.next_u64(); traits = API-IND-001.</t>
+          <t xml:space="preserve">1. Refuse if locked.
+2. seed = rng.next_u64(); (traits, quirks) = API-IND-001(sp, seed).</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -4332,7 +4382,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>ALG-12: clone each agent into an empty SimWorld with only its shelter/water; place stimulus by distance/side/wind; fixed seed; tick 10 s in fixed steps of FIXED_DT (PF-08); record segments.</t>
+          <t xml:space="preserve">ALG-12: clone each agent alone into a SimWorld with the same species table and the terrain within 80 m; place stimulus by distance/side/wind; fixed seed; tick 10 s in fixed steps of FIXED_DT (PF-08); record segments.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -4364,7 +4414,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>fn rename_agent(a: &amp;mut Agent, name: &amp;str)</t>
+          <t xml:space="preserve">fn rename_agent(a: &amp;mut Agent, name: &amp;str) -&gt; Result&lt;(), NameError&gt;</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -4379,12 +4429,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. 1–24 chars.</t>
+          <t xml:space="preserve">1. Trim; 1–40 chars (UI-07).</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>NameError</t>
+          <t xml:space="preserve">NameError → MSG-029</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -4616,10 +4666,9 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. compile (API-BRN-002).
-2. Embed used activities.
-3. ron::ser::to_string_pretty with schema_version = CURRENT.
-4. File name = snake_case(name) + ".noetic.ron".</t>
+          <t xml:space="preserve">1. Embed the used activities (sp.brain is already compiled by the editor, API-BRN-002).
+2. ron::ser::to_string_pretty with schema_version = CURRENT.
+3. File name = snake_case(name) + ".noetic.ron".</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -4651,7 +4700,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>fn parse_species(text: &amp;str) -&gt; Result&lt;SpeciesFile, ParseError&gt;</t>
+          <t xml:space="preserve">fn parse_species(text: &amp;str) -&gt; Result&lt;Species, ImportError&gt;</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4661,18 +4710,19 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>SpeciesFile</t>
+          <t xml:space="preserve">Species</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. Size ≤ 2 MB; ron::from_str with deny_unknown_fields.
-2. Map error to ParseError{line, col, msg}.</t>
+          <t xml:space="preserve">1. Size ≤ 2 MB; read as ron::Value (ParseError{line, col, msg} on bad syntax).
+2. Migrate the Value to CURRENT (API-IO-004); a missing schema_version counts as 0.
+3. Deserialize into Species with deny_unknown_fields.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>ParseError → MSG-013</t>
+          <t xml:space="preserve">ImportError::Parse → MSG-013 (with line and column); ImportError::Migrate → MSG-025</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -4699,7 +4749,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>fn validate_species(f: &amp;mut SpeciesFile) -&gt; Vec&lt;Warning&gt;</t>
+          <t xml:space="preserve">fn validate_species(f: &amp;mut Species) -&gt; Result&lt;Vec&lt;Warning&gt;, ValidateError&gt;</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4719,7 +4769,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Hard errors → Err</t>
+          <t xml:space="preserve">ValidateError → MSG-013; warnings → MSG-031 in DLG-03-03</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -4767,7 +4817,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>MigrateError::Unsupported</t>
+          <t xml:space="preserve">MigrateError::Unsupported, returned to the caller (MSG-025 on import, MSG-027 on project load)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -4809,7 +4859,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. API-IO-002/004/003.
+          <t xml:space="preserve">1. API-IO-002 (it migrates with API-IO-004), then API-IO-003.
 2. Name clash → "&lt;name&gt; (2)".
 3. Activities merged by name (same content) or added.
 4. Build graph; MSG-012.</t>
@@ -4817,7 +4867,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>MSG-013</t>
+          <t xml:space="preserve">MSG-013, MSG-025, MSG-031</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -4865,7 +4915,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>ClipError → select text + "use Ctrl+C"</t>
+          <t xml:space="preserve">ClipError → select the text + MSG-028</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -4892,7 +4942,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>fn save_file_dialog(default_name: &amp;str, text: &amp;str)</t>
+          <t xml:space="preserve">fn save_file_dialog(default_name: &amp;str, text: &amp;str) -&gt; Result&lt;(), IoError&gt;</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4912,12 +4962,12 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>IoError → toast</t>
+          <t xml:space="preserve">IoError → MSG-026</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>DLG-02-03</t>
+          <t xml:space="preserve">DLG-02-04</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -5326,7 +5376,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>fn update_needs(a: &amp;mut Agent, sp: &amp;Species, dt_h: f32)</t>
+          <t xml:space="preserve">fn update_needs(a: &amp;mut Agent, sp: &amp;Species, view: &amp;dyn WorldView, dt: f32, dt_h: f32)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -5420,7 +5470,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>fn update_memory(a: &amp;mut Agent, p: &amp;Percepts, dt: f32, forget: bool)</t>
+          <t xml:space="preserve">fn update_memory(a: &amp;mut Agent, p: &amp;Percepts, dt: f32, dt_h: f32, forget: bool)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -5562,7 +5612,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>fn weighted_pick&lt;T: Copy&gt;(items: &amp;[(T, u8)], rng: &amp;mut Rng) -&gt; Option&lt;T&gt;</t>
+          <t xml:space="preserve">fn weighted_pick&lt;T&gt;(items: &amp;[(T, u8)], rng: &amp;mut Rng) -&gt; Option&lt;&amp;T&gt;</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -5657,7 +5707,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>fn choose_activity(a: &amp;mut Agent, sp: &amp;Species, acts: &amp;Activities, hour: f32, out: &amp;mut Outbox) -&gt; (ActivityId, Scores)</t>
+          <t xml:space="preserve">fn choose_activity(a: &amp;mut Agent, sp: &amp;Species, hour: f32, out: &amp;mut Outbox) -&gt; (ActivityId, Scores)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -5672,7 +5722,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>ALG-10 with a.rng; hour = view.hour().
+          <t xml:space="preserve">ALG-10 with a.rng; think_agent passes hour = view.hour(); options are looked up in sp.activities; runs only while the state is Choosing.
 Chose goes to out.events.</t>
         </is>
       </c>
@@ -5850,7 +5900,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>fn fight(a: &amp;mut Agent, view: &amp;dyn WorldView, dt: f32, out: &amp;mut Outbox)</t>
+          <t xml:space="preserve">fn fight(a: &amp;mut Agent, view: &amp;dyn WorldView, dt: f32, dt_h: f32, out: &amp;mut Outbox)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -5865,8 +5915,8 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>ALG-11 for one side.
-Damage and the challenge go to out; the rival answers in its own think.</t>
+          <t xml:space="preserve">ALG-11 for one side.
+Damage and the challenge go to out; the rival answers in its own act.</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -6041,7 +6091,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>pub struct Rng(Pcg32); fn seed(u64), next_u32, unit() -&gt; f32, range(a,b), below(n)</t>
+          <t xml:space="preserve">pub struct Rng(Pcg32); fn seed(u64), next_u32, next_u64, unit() -&gt; f32, range(a,b), below(n)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -6056,7 +6106,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>1. Pcg32 seeded from agent seed ⊕ species hash.
+          <t xml:space="preserve">1. A live agent's Pcg32 is seeded from agent seed ⊕ species hash; the sandbox reseeds its copy with seed ^ 0x5EED (ALG-12) and personality uses its own Rng::seed(seed) (ALG-09).
 2. No global RNG anywhere in core.</t>
         </is>
       </c>
@@ -6089,7 +6139,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>fn routine_factor(r: Routine, hour: f32) -&gt; f32</t>
+          <t xml:space="preserve">fn routine_factor(r: Routine, hour: f32, is_rest: bool) -&gt; f32</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -6189,7 +6239,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>dt = THINK_DT (s)</t>
+          <t xml:space="preserve">dt = THINK_DT = stride × FIXED_DT (PF-08)</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -6199,9 +6249,9 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>1. Skip if Dead (PRC-02).
+          <t xml:space="preserve">1. Skip if Dead (PRC-02).
 2. In this order: heal, update_needs, perceive, update_memory, update_fear, threat_branch, choose_activity (PRC-03…10).
-3. dt_h = dt / secs_per_game_hour for the per-hour rates.
+3. dt_h = dt / view.secs_per_game_hour(), hour = view.hour(), forget = view.forget(); choose_activity runs only while Choosing.
 4. Writes only a; effects for other agents and SimEvents go to out.</t>
         </is>
       </c>
@@ -6234,7 +6284,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>pub fn act_agent(a: &amp;mut Agent, sp: &amp;Species, view: &amp;dyn WorldView, dt: f32, out: &amp;mut Outbox) -&gt; Movement</t>
+          <t xml:space="preserve">pub fn act_agent(a: &amp;mut Agent, sp: &amp;Species, view: &amp;dyn WorldView, dt: f32, move_failed: bool, out: &amp;mut Outbox) -&gt; Movement</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -6249,8 +6299,8 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>1. Skip if Dead.
-2. In this order: run_step, follow_group, fight, leave_mark, locomotion (PRC-11…15).
+          <t xml:space="preserve">1. Skip if Dead.
+2. Reacting: t_left −= dt (ALG-06 picks the next reaction once it is over). Otherwise, in this order: run_step, follow_group, fight, leave_mark, locomotion (PRC-11…15).
 3. Writes only a; damage, challenges and marks go to out.</t>
         </is>
       </c>
@@ -6298,9 +6348,9 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>1. Alarm → propagate_alarm (ALG-08).
+          <t xml:space="preserve">1. Alarm → propagate_alarm (ALG-08).
 2. Damage → apply_damage (ALG-11b).
-3. Challenge → remember the rival; its next think fights back or flees (ALG-11).
+3. Challenge → remember the rival; its next act fights back or flees (ALG-11).
 4. The host picks the receivers in id order and stores Mark itself.</t>
         </is>
       </c>
@@ -6542,7 +6592,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API-IO-002/004/003.
+          <t xml:space="preserve">1. API-IO-002 (it migrates with API-IO-004), then API-IO-003.
 2. Return asset; warnings logged.</t>
         </is>
       </c>
@@ -6637,7 +6687,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. Spatial grid (cell 8 m) of world features and agents.
+          <t xml:space="preserve">1. Advance NoeticClock one fixed step (PRC-01); then the spatial grid (cell 8 m) of world features, agents and ScentMark entities (marks_near).
 2. Player/noise stimuli.
 3. Marker zones (Cover, Mud…) answer terrain_at; unmarked ground is open.
 4. Agent positions read back from Transform: the game moved them.
@@ -6882,13 +6932,13 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. app.register_noetic_action::&lt;T&gt;() stores factory + metadata.
+          <t xml:space="preserve">1. noetic::plugin adds app.register_noetic_action::&lt;T&gt;(), which stores factory + metadata in ExtRegistry (the type stays Bevy-free in core).
 2. Metadata exported to editor via BRP/JSON.</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Duplicate id → panic at startup</t>
+          <t xml:space="preserve">Duplicate id → Err(ExtError::Duplicate) (ERR-14), logged; the first registration stays</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -6978,9 +7028,9 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1. Merge every agent Effect buffer; sort by (source id, seq).
+          <t xml:space="preserve">1. Merge every agent Effect buffer; sort by (source id, seq).
 2. Receivers in id order: alarm → agents in its radius (WorldViewCache); damage and challenge → their target; apply_effect (API-COR-022).
-3. Mark → spawn a ScentMark entity; decay despawns it at strength 0.
+3. Mark → spawn a ScentMark entity; afterwards every ScentMark ages (API-COR-015) and is despawned at strength 0.
 4. Alarm → NoeticAlarm for the game.</t>
         </is>
       </c>
@@ -7054,15 +7104,21 @@
     <row r="5" ht="116.5" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>for need in Need::ALL {                       // fixed order
-    a.needs[need] += sp.needs.rate(need) * dt_h;             // per game hour
-}
-if let InActivity { act, step, .. } = a.state {
-    let k = step.kind.recovers();                             // e.g. Eat → (Hunger, 8.0/s)
-    if let Some((need, per_s)) = k { a.needs[need] -= per_s * dt_s; }
-}
-a.needs.clamp_all(0.0, 100.0);
-// trait effects: Appetite scales hunger rate × (0.6 + appetite/100 × 0.8); Energy scales fatigue × (1.4 − energy/100 × 0.8)</t>
+          <t xml:space="preserve">// rate needs, per game hour (dt_h)
+a.needs[Hunger]  += sp.needs.hunger_per_h * (0.6 + a.traits.appetite as f32 / 125.0) * dt_h;
+a.needs[Thirst]  += sp.needs.thirst_per_h * dt_h;
+if !resting { a.needs[Fatigue] += sp.needs.fatigue_per_h * (if active_hours { 1.0 } else { 1.6 }) * (1.3 - a.traits.energy as f32 / 150.0) * dt_h; }
+// needs driven by the hour or the place (hour = view.hour())
+a.needs[Heat]    += (if (10.5..16.5).contains(&amp;hour) { 40.0 } else { -30.0 }) * dt_h;
+a.needs[Sing]    += (if (5.0..10.0).contains(&amp;hour) || (16.0..19.0).contains(&amp;hour) { 90.0 } else { -50.0 }) * dt_h;
+a.needs[Safety]  += (if near_shelter_or_own_safe_mark(a, view, 6.0) { 10.0 } else { -2.0 }) * dt;   // per second
+a.needs[Company] += (if group_member_within(a, view, 15.0) { -40.0 } else { 20.0 }) * dt_h;     // group species only
+a.needs.clamp_all(0.0, 100.0);                     // an activity lowers its need in run_step (API-COR-011)
+// driving values for ALG-10, drive(a, sp, need, hour):
+//   Hunger, Thirst, Heat, Sing, Company → the need · Fatigue → need + 55 outside active hours + 35 if limping
+//   Safety → 100 − safety · Fear → 25 + a.fear × 0.8 · Calm → (100 − a.fear) × 0.55
+//   Curiosity → 20 + curiosity × 0.6 · Boredom → 30 + energy × 0.2 · Mark → time since last_mark / every_min × 100 (0 if marks are off)
+//   Fight → fight_urge (ALG-11) with a rival within 25 m, else 0 · quirks may add +20 (e.g. "keeps watch more than others")</t>
         </is>
       </c>
     </row>
@@ -7076,11 +7132,11 @@
     <row r="8" ht="229" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>// for each stimulus/agent s within max(vision, hearing, smell) using the spatial grid
+          <t xml:space="preserve">// for each stimulus/agent s within max(vision, hearing, smell) using the spatial grid
 let d = dist(a.pos, s.pos);
 // vision
 let in_cone  = angle_between(a.heading, s.pos - a.pos) &lt;= sp.senses.angle / 2.0;
-let light_k  = lerp(sp.senses.night_vision, 1.0, world.light());          // 0.05..1
+let light_k  = lerp(sp.senses.night_vision, 1.0, view.light());          // night_vision..1
 let range_v  = sp.senses.vision * light_k;
 let motion   = match s.motion { Still =&gt; 0.6, Walk =&gt; 1.0, Run =&gt; 1.3 };
 let cover    = if s.in_tall_grass &amp;&amp; s.motion == Still { 0.35 } else { 1.0 };
@@ -7089,10 +7145,10 @@
 let r_h = sp.senses.hearing.min(s.loudness);
 let h = if r_h &gt; 0.0 { (1.0 - d / r_h).clamp(0.0, 1.0) } else { 0.0 };
 // smell: wind carries scent from s to a
-let cos_w = world.wind().dir.dot((a.pos - s.pos).normalize());
+let cos_w = view.wind().dir.dot((a.pos - s.pos).normalize());
 let r_s = sp.senses.smell * (0.3 + 0.7 * cos_w.max(0.0));
 let m = (1.0 - d / r_s).clamp(0.0, 1.0);
-let strength = v.max(h).max(m) * (1.0 - a.memory.habituation(s.kind));     // 0..1
+let strength = v.max(h).max(m).min(1.0) * (1.0 - a.memory.habituation(s.kind));     // 0..1
 percepts.best = percepts.best.max(strength);</t>
         </is>
       </c>
@@ -7107,10 +7163,11 @@
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>// habituation to a visible, still player while calm: +0.02/s up to 0.8; running player: −0.3 at once
+          <t xml:space="preserve">// habituation to a visible, still player while calm: +0.02/s up to 0.8; running player: −0.3 at once
 // scare spot: on Reacting start push (pos, strength 1.0); strength −= 1/24 per game hour if forget
 // remembered water / shelter / own marks: last seen position, refreshed when perceived
-// fear near a scare spot (≤ 10 m) gets +20% gain</t>
+// fear near a scare spot (≤ 10 m) gets +20% gain (ALG-05)
+// alarm: remembered with its source; strength −= 1/6 per game hour (dt_h)</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7181,8 @@
     <row r="14" ht="66.5" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>let gain  = percepts.best * (0.4 + a.traits.fear as f32 / 100.0 * 1.2) * 60.0 * dt;   // from prototype
+          <t xml:space="preserve">let mut gain = percepts.best * (0.4 + a.traits.fear as f32 / 100.0 * 1.2) * 60.0 * dt;   // from prototype
+if a.memory.scare_spot_near(a.pos, 10.0) { gain *= 1.2; }      // ALG-04
 let mut decay = 8.0 * (0.5 + (100.0 - a.traits.fear as f32) / 100.0);
 if view.marks_near(a.pos, 6.0).iter().any(|m| m.species == a.species &amp;&amp; m.meaning == Meaning::Safe) { decay *= 1.5; }
 a.fear = (a.fear + gain - decay * dt).clamp(0.0, 100.0);
@@ -7142,15 +7200,18 @@
     <row r="17" ht="141.5" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>match a.state {
-  Reacting { node, t_left } if t_left &gt; 0.0 =&gt; { /* keep reacting */ }
-  Reacting { node, .. } =&gt; match weighted_pick(&amp;brain.threat.reactions[node].next, &amp;mut a.rng) {
-      Some(n) =&gt; start(a, n),                                   // emit Anim, set duration
-      None if a.fear &gt; sp.needs.fear_threshold =&gt; start(a, node), // keep last reaction (e.g. hide)
-      None =&gt; a.state = Choosing,
+          <t xml:space="preserve">match a.state {
+  Reacting { t_left, .. } if t_left &gt; 0.0 =&gt; { /* act_agent counts t_left down */ }
+  Reacting { node, .. } =&gt; match sp.brain.threat.reactions.get(&amp;node) {
+      None =&gt; a.state = Choosing,                                   // unknown node: V-02 prevents it, core never panics
+      Some(r) =&gt; match weighted_pick(&amp;r.next, &amp;mut a.rng) {
+          Some(n) =&gt; start(a, n.clone()),                           // emit Anim, set duration
+          None if a.fear &gt; sp.needs.fear_threshold =&gt; start(a, node), // keep the last reaction (e.g. hide)
+          None =&gt; a.state = Choosing,
+      },
   },
-  _ if a.fear &gt; sp.needs.fear_threshold =&gt; if let Some(n) = weighted_pick(&amp;brain.threat.first, &amp;mut a.rng) { start(a, n) },
-  _ =&gt; {}
+  Choosing | InActivity { .. } if a.fear &gt; sp.needs.fear_threshold =&gt; if let Some(n) = weighted_pick(&amp;sp.brain.threat.first, &amp;mut a.rng) { start(a, n.clone()) },
+  _ =&gt; {}                                                           // Fighting ends in ALG-11; Dead never thinks
 }
 // duration: Freeze{secs} × (1.4 − fear/100 × 0.8) (fearful animals freeze shorter and flee sooner)</t>
         </is>
@@ -7191,11 +7252,11 @@
     <row r="23" ht="66.5" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>let sum: u32 = items.iter().map(|(_, w)| *w as u32).sum();
+          <t xml:space="preserve">let sum: u32 = items.iter().map(|(_, w)| *w as u32).sum();
 if sum == 0 { return None; }
 let mut r = rng.below(sum);
-for (t, w) in items { if r &lt; *w as u32 { return Some(*t); } r -= *w as u32; }
-unreachable!()</t>
+for (t, w) in items { if r &lt; *w as u32 { return Some(t); } r -= *w as u32; }
+None // not reached while r &lt; sum; core never panics (EP-01)</t>
         </is>
       </c>
     </row>
@@ -7209,13 +7270,12 @@
     <row r="26" ht="92" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>// radius and reach: Thump 15 m (same species ×1, others ×0.5) · TailFlag 40 m (own group) · Chirp 35 m (all species)
-// run by apply_effect (API-COR-022) for each queued Effect::Alarm, receivers in id order
-for b in world.neighbours(src.pos, radius) {
-    let k = (1.0 - dist / radius) * reach(kind, b.species == src.species) * (0.5 + b.traits.fear as f32 / 100.0);
-    b.fear = (b.fear + 60.0 * k).min(100.0);
-    b.memory.push_alarm(src.id, now);
-}</t>
+          <t xml:space="preserve">// radius and reach: Thump 15 m (same species ×1, others ×0.5) · TailFlag 40 m (same species only) · Chirp 35 m (all species)
+// one receiver b at distance dist from src; apply_effect (API-COR-022) calls this for each agent in the radius, in id order
+let (radius, k_reach) = reach(kind, same_species);          // k_reach 0.0 → b ignores this alarm
+let k = (1.0 - dist / radius).max(0.0) * k_reach * (0.5 + b.traits.fear as f32 / 100.0);
+b.fear = (b.fear + 60.0 * k).min(100.0);
+b.memory.push_alarm(src);                                   // memory ages it (ALG-04)</t>
         </is>
       </c>
     </row>
@@ -7229,13 +7289,14 @@
     <row r="29" ht="91.5" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>let mut rng = Rng::seed(seed);
+          <t xml:space="preserve">let mut rng = Rng::seed(seed);
 for t in Trait::ALL {                                // fixed order: fear, curiosity, social, appetite, energy, stubborn, aggro
-    let (mean, var) = base.get(t);
+    let mean = sp.personality.base.get(&amp;t).copied().unwrap_or(50);
+    let var = sp.personality.variation.get(&amp;t).copied().unwrap_or(0);
     let v = mean as f32 + var as f32 * (2.0 * rng.unit() - 1.0);
     traits.set(t, v.round().clamp(0.0, 100.0) as u8);
 }
-let n_quirks = 1 + rng.below(2);                    // 1–2 quirks from the species pool, no duplicates</t>
+let n_quirks = if sp.quirks.is_empty() { 0 } else { 1 + rng.below(2) };   // 1–2 from sp.quirks, no duplicates, none if empty</t>
         </is>
       </c>
     </row>
@@ -7249,16 +7310,17 @@
     <row r="32" ht="129" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>// curve(x), x = need/100:  Linear x · Accelerating x² · FastStart √x · Step (x ≥ 0.6) as 1/0
-for act in &amp;sp.brain.choose.options {
-    let x = a.needs[act.need] / 100.0;
-    let mut s = curve_eval(act.curve, x) * act.weight * routine_factor(sp.routine, hour, act.is_rest());
+          <t xml:space="preserve">// curve(x), x = need/100:  Linear x · Accelerating x² · FastStart √x · Step (x ≥ 0.6) as 1/0
+for name in &amp;sp.brain.choose.options {
+    let Some(act) = sp.activities.get(name) else { continue };   // V-02 keeps this rare; core never panics
+    let x = drive(a, sp, act.need, hour) / 100.0;           // driving values of ALG-02
+    let mut s = curve_eval(act.curve, x) * act.weight * routine_factor(sp.routine, hour, act.need == Need::Fatigue);
     s *= trait_factor(act, &amp;a.traits);              // appetite → food, curiosity → explore, energy → rest (inverse), social → group
-    s *= 1.0 + quirk_bonus(act, &amp;a.quirks);         // e.g. "prefere trevo": +0.2 for graze on clover
+    s *= 1.0 + quirk_bonus(act, &amp;a.quirks);         // e.g. "likes clover": +0.2 for graze on clover
     s *= 1.0 + sp.brain.choose.noise * (2.0 * a.rng.unit() - 1.0);
-    scores.push((act.id, s));
+    scores.push((name.clone(), s));
 }
-// highest score wins; tie → lower ActivityKey (deterministic)</t>
+// highest score wins; tie → lower ActivityId (the String key) (deterministic)</t>
         </is>
       </c>
     </row>
@@ -7272,10 +7334,10 @@
     <row r="35" ht="67" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>// a and the rival each run fight() in their own act; damage and the challenge cross over as Effects (API-COR-022)
+          <t xml:space="preserve">// a and the rival each run fight() in their own act; damage and the challenge cross over as Effects (API-COR-022)
 // urge to fight rises +aggro/100 × 6 per game hour; ≥ 70 and same-species rival ≤ 12 m → GoToRival → Scuffle
-// each scuffle round (1.5–3 s): dmg = (2.0 + aggro/20) × rng.range(0.7, 1.3) to the other
-// opponent: fights back if stubborn + aggro &gt; 90 + rng.below(40), otherwise flees (Reacting: Flee)
+// each scuffle round (1.5–3 s): dmg = (2.0 + aggro/20) × a.rng.range(0.7, 1.3) to the other
+// opponent: fights back if stubborn + aggro &gt; 90 + a.rng.below(40), otherwise flees (Reacting: Flee)
 // loser = lower health ratio at the end; winner's urge resets to 0; failed approach → cooldown 60 s</t>
         </is>
       </c>
@@ -7290,7 +7352,8 @@
     <row r="38" ht="66.5" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>a.health -= dmg;
+          <t xml:space="preserve">if a.state == Dead { return; }                       // already dead: no second Died
+a.health -= dmg;
 a.fear = (a.fear + dmg * (1.0 - sp.health.pain_resist) * 2.0).min(100.0);
 a.limping = a.health / sp.health.max &lt; sp.health.limp_below;      // speed × 0.6
 if a.health &lt;= 0.0 { a.state = Dead; out.events.push(SimEvent::Died { agent: a.id }) }
@@ -7308,14 +7371,16 @@
     <row r="41" ht="129" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>let mut results = vec![];
+          <t xml:space="preserve">let mut results = vec![];
 for id in peers {                                       // each animal alone
     let mut w = SimWorld::empty_like(src);              // same species table, terrain within 80 m, no other agents
-    let mut a = src.agent(id).clone(); a.state = Choosing; a.fear = 0.0; a.rng = Rng::seed(a.seed ^ 0x5EED);
+    let Some(a0) = src.agent(id) else { continue }; let mut a = a0.clone(); a.state = Choosing; a.fear = 0.0; a.rng = Rng::seed(a.seed ^ 0x5EED);
     let pos = a.pos + dir(side, a.heading) * stimulus.dist; w.add_stimulus(stimulus.at(pos, wind));
     w.agents.push(a);
+    let mut segs = vec![];
     for _ in 0..(secs / FIXED_DT) as usize { tick(&amp;mut w, FIXED_DT); record_segment(&amp;w, id, &amp;mut segs); }
-    results.push(SandboxResult { id, segs, reacted: segs.iter().any(|s| s.is_reaction) });
+    let reacted = segs.iter().any(|s| s.is_reaction);
+    results.push(SandboxResult { id, segs, reacted });
 }
 // the source world is never borrowed mutably</t>
         </is>
@@ -7331,10 +7396,10 @@
     <row r="44" ht="106.5" customHeight="1">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>// intent: Noetic decides where and how; it never writes a.pos (the game, or the editor mover, moves the body)
+          <t xml:space="preserve">// intent: Noetic decides where and how; it never writes a.pos (the game, or the editor mover, moves the body)
 let base = if fleeing { sp.locomotion.flee_speed } else { sp.locomotion.speed };
 let speed = base * if a.limping { 0.6 } else { 1.0 };
-// Zigzag (flee) → the target shifts ± 35° sideways every rng.range(0.6, 1.0) s, so the mover only follows it
+// Zigzag (flee) → the target shifts ± 35° sideways every a.rng.range(0.6, 1.0) s, so the mover only follows it
 Movement { target: step target, gait: from the step and species (hop, walk, trot, run, zigzag, fly…), speed, gaze: strongest percept }
 // simple mover, editor SimWorld only (sim::tick):
 let terrain = match world.terrain_at(a.pos) { River =&gt; 0.5, Hill =&gt; 0.75, Mud =&gt; 0.8, _ =&gt; 1.0 };   // birds: 1.0
@@ -7374,7 +7439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7568,6 +7633,94 @@
       <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Coherence review: per-agent functions write an Outbox (TYP-24) for effects and SimEvents; threat_branch and choose_activity use a.rng (COR-006, 009, 011, 013…015, 020…022); perceive, update_fear and follow_group take &amp;dyn WorldView; the group leader is derived, never elected; ALG-05 uses view.marks_near; sandbox ticks fixed_dt (ALG-12, IND-008); quick_test takes the world and an id; SIM-005 secs_per_game_hour; RT-001 registers Apply and all three events; RT-006 drains the Outbox; English UI leftovers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Individuals are saved: API-PRJ-008 takes the SimWorld and writes its individuals; API-PRJ-009 respawns them from their seed and restores the edits; API-PRJ-012 restarts the timer when an individual is spawned or edited and saves at once on exit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review against the other documents: new API-BRN-026 create_activity for SCR-02-08 (144 APIs); validate_species returns a Result; parse and validate use Species, written as NoeticSpecies; Rng next_u64; no panic in core (RT-009, ALG-07b); BRN-003/005 messages and SelfLoop; drag_wire in PreUpdate; set_speed and sim_host_system run speed steps per fixed step through the accumulator; place_stimulus uses a core player stimulus; spawn_agent derives the leader; every user-facing error has a MSG (023…030); one name rule; fear threshold f32; UT-023 angle; the shortcut map covers KEY-04/07; MSG-007/022 shown where the External Design says; the context_menu and quick_test fn names match their APIs; English leftovers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each document checked against itself: files are read as ron::Value, migrated, then deserialized (IO-002, IO-005, RT-002, PRJ-009); export no longer calls the editor compiler (IO-001); load_project, delete_item, follow_agent and create_species take the SimHost; undo takes the toast token; update_activity, rename_agent and save_file_dialog return their errors; select_agent hit-tests a position; generate_personality takes the species and returns the quirks; routine_factor takes is_rest; weighted_pick returns a reference; update_needs gets dt; ALG-02/03/05/06/08/10/11/12/13 match their APIs and fields (no index panic in ALG-06, ALG-08 per receiver, TailFlag same species); rates per Need, Locomotion struct, ScentMarks struct; DLG-02-04 Save…; SIM APIs move to noetic_editor::sim_host; ExtRegistry registered by noetic::plugin; MSG-007/008/009/029 raisers; logo_and_brand and species_tab fn names; 0.9 now names the two fn renames it made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="68" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.11</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs follow the prototype (ALG-02 rates and drivers, ALG-10 drive values; update_needs gets the view); a reaction counts down in act_agent and repeats or ends without panicking (ALG-06); the rival answers in its act (COR-022); act_agent gets move_failed; update_memory and fight get dt_h; think_agent reads secs_per_game_hour, forget and hour from the view; choose_activity uses sp.activities and runs only while Choosing; parse_species returns ImportError (Parse → MSG-013, Migrate → MSG-025); MSG-031 import fixes; KEY-12 redo; select_agent takes a Pick; spawn_agent returns Option; locate_agent gets its state and world; graph edits recompile through the command wrapper; ALG-03 clamps strength; ALG-09, 11b, 12 fixed; scent marks age in Apply and reach the WorldViewCache; type aliases in 6.1; counts 26 APIs and 196 items.</t>
         </is>
       </c>
     </row>
@@ -7628,13 +7781,13 @@
     <row r="5" ht="329" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>#[derive(Serialize, Deserialize, Clone, Debug)]
-#[serde(deny_unknown_fields)]
-pub struct NoeticSpecies {
+          <t xml:space="preserve">#[derive(Serialize, Deserialize, Clone, Debug)]
+#[serde(deny_unknown_fields, rename = "NoeticSpecies")]
+pub struct Species {
     pub schema_version: u32,
     pub species: String,
     pub color: Srgb8,                                   // "#RRGGBB"
-    pub locomotion: Locomotion,                         // Ground { hop, speed, flee_speed } | Bird { speed, flee_speed }
+    pub locomotion: Locomotion,                         // kind: Ground | Bird, hop, speed, flee_speed
     pub group: GroupKind,                               // Solitary | Group { leader: bool } | Flock
     pub shelter: Shelter,                               // Burrow | Bush | Tree
     pub routine: Routine,                               // Diurnal | Crepuscular | Nocturnal | MorningAfternoon
@@ -7643,7 +7796,7 @@
     pub health: HealthSpec,                             // max, pain_resist, heal_per_h, limp_below
     pub personality: PersonalityBase,                   // base: BTreeMap&lt;Trait,u8&gt;, variation: BTreeMap&lt;Trait,u8&gt;
     #[serde(default)] pub quirks: Vec&lt;String&gt;,
-    #[serde(default)] pub scent_marks: Vec&lt;MarkSpec&gt;,   // kind, meaning, every_min, lasts_h
+    #[serde(default)] pub scent_marks: ScentMarks,      // enabled, kinds, meaning, every_min, lasts_h
     pub brain: Brain,
     pub activities: BTreeMap&lt;String, Activity&gt;,
     #[serde(default)] pub animation_clips: BTreeMap&lt;String, String&gt;,
@@ -7652,6 +7805,7 @@
 pub struct ThreatBranch { pub first: Vec&lt;(String, u8)&gt;, pub reactions: BTreeMap&lt;String, ReactionNode&gt; }
 pub struct ReactionNode { #[serde(rename = "do")] pub do_: Reaction, #[serde(default)] pub next: Vec&lt;(String, u8)&gt; }
 pub struct ChooseSpec { pub noise: f32, pub options: Vec&lt;String&gt; }
+pub type NodeKey = String; pub type ActivityId = String; pub type WeightedRef = (NodeKey, u8); pub type SecsRange = (f32, f32);
 pub struct Activity { pub need: Need, pub curve: Curve, pub weight: f32, pub steps: Vec&lt;Step&gt; }
 pub struct Step { #[serde(rename = "do")] pub do_: StepKind, pub secs: (f32, f32), #[serde(default)] pub anim: Option&lt;String&gt; }</t>
         </is>
@@ -7660,7 +7814,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>6.2 Field table (FieldSpec) — every editable species field</t>
+          <t xml:space="preserve">6.2 Field table (FieldSpec) — the editable species fields with a range or a default</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8413,7 @@
     <row r="24" ht="29" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>needs.hunger/thirst/fatigue_per_h</t>
+          <t xml:space="preserve">needs.hunger/thirst/fatigue_per_h</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -8279,7 +8433,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>25 / 30 / 12</t>
+          <t xml:space="preserve">25 / 30 / 12</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -8444,7 +8598,7 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">false (templates: true)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -8773,7 +8927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9009,7 +9163,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>dialog inline text</t>
+          <t xml:space="preserve">graph toolbar chip (API-BRN-023)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -9058,7 +9212,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>API-PRJ-005, API-WLD-011</t>
+          <t xml:space="preserve">API-PRJ-005, API-WLD-011, API-BRN-009</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -9166,7 +9320,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>API-IO-002</t>
+          <t xml:space="preserve">API-IO-002, API-IO-003, API-IO-005</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -9414,12 +9568,255 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>dialog inline text</t>
+          <t xml:space="preserve">API-APP-006 show_toast (button inside the toast)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Button</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.graph.wrong_kind</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-BRN-005</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-APP-006 show_toast</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-024</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.graph.already_connected</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-BRN-005</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-APP-006 show_toast</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.import.newer_schema</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-IO-002, API-IO-005</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog inline text</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.file.save_failed</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-PRJ-008, API-IO-007</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-APP-006 show_toast</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-027</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.project.load_failed</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-PRJ-009</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-APP-006 show_toast</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-028</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.copy.failed</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-IO-006</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog inline text</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.name.invalid</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-PRJ-002, API-BRN-013, API-IND-009, API-SPC-002, API-SPC-006</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inline text at the field</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-030</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.species.rerolled</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-SPC-008</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-APP-006 show_toast</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msg.import.warnings</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-IO-003</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog inline text</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline</t>
         </is>
       </c>
     </row>
@@ -10256,12 +10653,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>target behind rabbit (angle 340°) at 10 m</t>
+          <t xml:space="preserve">target 160° off the heading at 10 m (rabbit angle 340°)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>vision &gt; 0 (rear blind spot only 20°)</t>
+          <t xml:space="preserve">vision &gt; 0 (the blind spot is the 20° straight behind)</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -11252,7 +11649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11279,7 +11676,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>143 APIs</t>
+          <t xml:space="preserve">144 APIs</t>
         </is>
       </c>
     </row>
@@ -11644,7 +12041,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>KEY-01…11</t>
+          <t xml:space="preserve">KEY-01…12</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -11699,7 +12096,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::world::host</t>
+          <t xml:space="preserve">noetic_editor::sim_host</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -11736,7 +12133,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::world::host</t>
+          <t xml:space="preserve">noetic_editor::sim_host</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -11773,7 +12170,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::world::host</t>
+          <t xml:space="preserve">noetic_editor::sim_host</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -11921,7 +12318,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::world::host</t>
+          <t xml:space="preserve">noetic_editor::sim_host</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -12052,7 +12449,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>SCR-02-08, POP-01-01</t>
+          <t xml:space="preserve">POP-01-01</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12597,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>(internal)</t>
+          <t xml:space="preserve">KEY-12</t>
         </is>
       </c>
     </row>
@@ -12227,12 +12624,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Atomic save of FMT-02.</t>
+          <t>Atomic save of FMT-02, individuals included.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>F-103, NFR-11</t>
+          <t>F-103, FR-402, FR-404, NFR-11</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -12866,7 +13263,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>SCR-02-08, SCR-03-09, SCR-03-12, SCR-03-13, SCR-03-15</t>
+          <t xml:space="preserve">SCR-03-09, SCR-03-12, SCR-03-13, SCR-03-15</t>
         </is>
       </c>
     </row>
@@ -13295,7 +13692,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>System (Update)</t>
+          <t xml:space="preserve">System (PreUpdate)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -13317,175 +13714,175 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-001</t>
+          <t xml:space="preserve">API-BRN-026</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>world_camera</t>
+          <t xml:space="preserve">create_activity</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::world::camera</t>
+          <t xml:space="preserve">noetic_editor::brain::activity</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Command</t>
+          <t xml:space="preserve">Command (undoable)</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Zoom, pan, fit of the world view.</t>
+          <t xml:space="preserve">Create an empty activity in the library.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>FR-202</t>
+          <t xml:space="preserve">FR-107</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>SCR-05-08, SCR-05-13, SCR-05-14</t>
+          <t xml:space="preserve">SCR-02-08</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>API-WLD-001</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>world_camera</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>noetic_editor::world::camera</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Zoom, pan, fit of the world view.</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>FR-202</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>SCR-05-08, SCR-05-13, SCR-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
           <t>API-WLD-002</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>minimap_click</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::world::minimap</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Move camera to clicked minimap point.</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>FR-202</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>SCR-05-12</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="29" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="62" ht="29" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>API-WLD-003</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>set_tool</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::world::tools</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>Select world tool and its hint.</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>FR-206</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>SCR-05-01, SCR-05-02, SCR-05-03, SCR-05-04, SCR-05-05, SCR-05-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>API-WLD-004</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>place_stimulus</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor::world::tools</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Test player, noise or food at a point.</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>FR-206</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>SCR-05-02, SCR-05-03, SCR-05-04</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-005</t>
+          <t>API-WLD-004</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>spawn_agent</t>
+          <t>place_stimulus</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::agent</t>
+          <t>noetic_editor::world::tools</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>fn</t>
+          <t>Command</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Create one animal.</t>
+          <t>Test player, noise or food at a point.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -13495,204 +13892,204 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>SCR-05-05, SCR-05-20, DLG-01-08</t>
+          <t>SCR-05-02, SCR-05-03, SCR-05-04</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>API-WLD-005</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>spawn_agent</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::agent</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Create one animal.</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>FR-206</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>SCR-05-05, SCR-05-20, DLG-01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
           <t>API-WLD-006</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>rotate_wind</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>noetic_core::world</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Rotate wind 45°.</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>FR-208</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>SCR-05-10</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="42" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>API-WLD-007</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>toggle_layer</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::world::layers</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Show/hide a debug layer.</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>FR-207</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>SCR-05-06, SCR-08-01, SCR-08-02, SCR-08-03, SCR-08-04, SCR-08-05, SCR-08-06</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>API-WLD-008</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>set_edit_mode</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::world::edit</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Enter/leave terrain edit mode.</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>FR-209, FR-210</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>SCR-05-07, SCR-07-04</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="29" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="68" ht="29" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>API-WLD-009</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>place_terrain</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::world::edit</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Command (undoable)</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>Place tree, bush, rock, burrow, pond, mud, tall grass, clover.</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>FR-209</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>SCR-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>API-WLD-010</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>transform_terrain</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor::world::edit</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Command (undoable)</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Move/resize item or river point.</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>FR-209</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>SCR-07-01, SCR-07-05</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-011</t>
+          <t>API-WLD-010</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>erase_terrain</t>
+          <t>transform_terrain</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -13707,29 +14104,29 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Delete a terrain item.</t>
+          <t>Move/resize item or river point.</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>FR-209, FR-210</t>
+          <t>FR-209</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>SCR-07-03</t>
+          <t>SCR-07-01, SCR-07-05</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-012</t>
+          <t>API-WLD-011</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>reset_world</t>
+          <t>erase_terrain</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -13744,29 +14141,29 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Restore default map.</t>
+          <t>Delete a terrain item.</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>FR-209</t>
+          <t>FR-209, FR-210</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>SCR-07-06</t>
+          <t>SCR-07-03</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-013</t>
+          <t>API-WLD-012</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>clear_terrain</t>
+          <t>reset_world</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -13781,7 +14178,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Remove all terrain items.</t>
+          <t>Restore default map.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -13791,93 +14188,93 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>SCR-07-07</t>
+          <t>SCR-07-06</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-014</t>
+          <t>API-WLD-013</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>select_agent</t>
+          <t>clear_terrain</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::world::tools</t>
+          <t>noetic_editor::world::edit</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Command</t>
+          <t>Command (undoable)</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Select animal (map click or list).</t>
+          <t>Remove all terrain items.</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>FR-211</t>
+          <t>FR-209</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>SCR-05-01, SCR-05-19</t>
+          <t>SCR-07-07</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-015</t>
+          <t>API-WLD-014</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>render_world</t>
+          <t>select_agent</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::world::view</t>
+          <t>noetic_editor::world::tools</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>System (Update)</t>
+          <t>Command</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Draw colored map, agents, labels, layers.</t>
+          <t>Select animal (map click or list).</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>FR-201, FR-213</t>
+          <t>FR-211</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>SCR-05-08</t>
+          <t>SCR-05-01, SCR-05-19</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-016</t>
+          <t>API-WLD-015</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>render_day_strip</t>
+          <t>render_world</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -13892,29 +14289,29 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Day bar, now marker and species activity lanes.</t>
+          <t>Draw colored map, agents, labels, layers.</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>FR-204</t>
+          <t>FR-201, FR-213</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>SCR-05-17, SCR-05-18</t>
+          <t>SCR-05-08</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>API-WLD-017</t>
+          <t>API-WLD-016</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>agent_list</t>
+          <t>render_day_strip</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -13924,326 +14321,326 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Builder</t>
+          <t>System (Update)</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Animals of the species with current action.</t>
+          <t>Day bar, now marker and species activity lanes.</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>FR-211</t>
+          <t>FR-204</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>SCR-05-19</t>
+          <t>SCR-05-17, SCR-05-18</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
+          <t>API-WLD-017</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>agent_list</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>noetic_editor::world::view</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Builder</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Animals of the species with current action.</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>FR-211</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>SCR-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
           <t>API-WLD-018</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>set_time_preset</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::world::view</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Morning 7h, noon 12h, afternoon 16h, night 22h.</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>FR-204</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>SCR-05-15</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>API-DBG-001</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>agent_debug_view</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::inspector</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>System (Update)</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>Fill the Details panel for the selected animal.</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>FR-211</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>SCR-06-01, SCR-06-04, SCR-06-05, SCR-06-06, SCR-06-07, SCR-06-08, SCR-06-09, SCR-06-10, SCR-06-11</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="29" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="79" ht="29" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>API-DBG-002</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>quick_test</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>noetic_core::agent</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>Thirst, hunger, tire, calm, injure, heal, noise nearby, scare.</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>FR-212</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>SCR-06-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>API-DBG-003</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>locate_agent</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor::world::camera</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Center the camera on the animal (switches to World).</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>FR-211</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>SCR-06-02, SCR-13-05</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
+          <t>API-DBG-003</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>locate_agent</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>noetic_editor::world::camera</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Center the camera on the animal (switches to World).</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>FR-211</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>SCR-06-02, SCR-13-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
           <t>API-DBG-004</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>deselect</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::world::tools</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>Clear selection.</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>SCR-06-03</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="107" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="82" ht="107" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>API-SPC-001</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>set_species_field</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::species::edit</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Command (undoable)</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Generic setter for every species control (color, movement, group, shelter, health, speeds, senses, rates, routine, marks…).</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>FR-304–FR-310</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>SCR-09-07, SCR-09-08, SCR-09-09, SCR-09-10, SCR-09-11, SCR-09-12, SCR-09-13, SCR-09-14, SCR-09-15, SCR-09-16, SCR-09-17, SCR-10-01, SCR-10-02, SCR-10-03, SCR-10-04, SCR-10-05, SCR-10-06, SCR-10-12, SCR-11-01, SCR-11-02, SCR-11-03, SCR-11-04, SCR-11-05, SCR-11-06</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="55" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="83" ht="55" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>API-SPC-002</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>create_species</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::species::create</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>Command (undoable)</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>Create from blank or template.</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>FR-303</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>SCR-02-02, DLG-01-01, DLG-01-02, DLG-01-03, DLG-01-04, DLG-01-05, DLG-01-06, DLG-01-07, DLG-01-08, DLG-01-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="29" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>API-SPC-003</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>duplicate_species</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor::species::create</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>Command (undoable)</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Same as API-PRJ-003 for species.</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>FR-301</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>SCR-09-04</t>
         </is>
       </c>
     </row>
     <row r="84" ht="29" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>API-SPC-004</t>
+          <t>API-SPC-003</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>delete_species</t>
+          <t>duplicate_species</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -14258,34 +14655,34 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Delete species and its animals.</t>
+          <t>Same as API-PRJ-003 for species.</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>FR-302</t>
+          <t>FR-301</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>SCR-09-05</t>
+          <t>SCR-09-04</t>
         </is>
       </c>
     </row>
     <row r="85" ht="29" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>API-SPC-005</t>
+          <t>API-SPC-004</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>apply_preset_species</t>
+          <t>delete_species</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::species::presets</t>
+          <t>noetic_editor::species::create</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -14295,29 +14692,29 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Apply preset to species base personality.</t>
+          <t>Delete species and its animals.</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>FR-309</t>
+          <t>FR-302</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>SCR-10-08</t>
+          <t>SCR-09-05</t>
         </is>
       </c>
     </row>
     <row r="86" ht="29" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>API-SPC-006</t>
+          <t>API-SPC-005</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>save_preset</t>
+          <t>apply_preset_species</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -14332,7 +14729,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Save current trait values as preset.</t>
+          <t>Apply preset to species base personality.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -14342,19 +14739,19 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>SCR-10-09, SCR-10-10, SCR-13-08</t>
+          <t>SCR-10-08</t>
         </is>
       </c>
     </row>
     <row r="87" ht="29" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>API-SPC-007</t>
+          <t>API-SPC-006</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>delete_preset</t>
+          <t>save_preset</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -14369,7 +14766,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Delete user preset (×).</t>
+          <t>Save current trait values as preset.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -14379,19 +14776,19 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>SCR-10-08</t>
+          <t>SCR-10-09, SCR-10-10, SCR-13-08</t>
         </is>
       </c>
     </row>
     <row r="88" ht="29" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>API-SPC-008</t>
+          <t>API-SPC-007</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>reroll_all</t>
+          <t>delete_preset</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -14406,34 +14803,34 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>New personalities for unlocked animals.</t>
+          <t>Delete user preset (×).</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>FR-309, FR-403</t>
+          <t>FR-309</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>SCR-10-11</t>
+          <t>SCR-10-08</t>
         </is>
       </c>
     </row>
     <row r="89" ht="29" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>API-SPC-009</t>
+          <t>API-SPC-008</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>set_anim_clip</t>
+          <t>reroll_all</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::species::model3d</t>
+          <t>noetic_editor::species::presets</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -14443,29 +14840,29 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Map an animation event to a model clip.</t>
+          <t>New personalities for unlocked animals.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>FR-311</t>
+          <t>FR-309, FR-403</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>SCR-12-02, SCR-12-03</t>
+          <t>SCR-10-11</t>
         </is>
       </c>
     </row>
     <row r="90" ht="29" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>API-SPC-010</t>
+          <t>API-SPC-009</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>animation_rows</t>
+          <t>set_anim_clip</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -14475,182 +14872,182 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>fn (pure)</t>
+          <t>Command (undoable)</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Collect animation events used by the species.</t>
+          <t>Map an animation event to a model clip.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>FR-312</t>
+          <t>FR-311</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>SCR-12-01, SCR-12-03, DLG-05-01</t>
+          <t>SCR-12-02, SCR-12-03</t>
         </is>
       </c>
     </row>
     <row r="91" ht="29" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>API-SPC-010</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>animation_rows</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>noetic_editor::species::model3d</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>fn (pure)</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Collect animation events used by the species.</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>FR-312</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>SCR-12-01, SCR-12-03, DLG-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="29" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
           <t>API-SPC-011</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>format_animation_list</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::species::model3d</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>fn (pure)</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>Markdown table or CSV (RFC 4180).</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>FR-312, FMT-03</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>DLG-05-02, DLG-05-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>API-SPC-012</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>species_tab</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor::species::view</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Switch Body / Mind / Routine / 3D tab.</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>FR-304</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>SCR-09-06</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>API-IND-001</t>
+          <t>API-SPC-012</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>generate_personality</t>
+          <t>species_tab</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::personality</t>
+          <t>noetic_editor::species::view</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>fn (pure)</t>
+          <t>Command</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Seeded traits from species mean ± variation.</t>
+          <t>Switch Body / Mind / Routine / 3D tab.</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>FR-401</t>
+          <t>FR-304</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>SCR-13-02</t>
+          <t>SCR-09-06</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>API-IND-002</t>
+          <t>API-IND-001</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>reroll_agent</t>
+          <t>generate_personality</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::individuals</t>
+          <t>noetic_core::personality</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Command (undoable)</t>
+          <t>fn (pure)</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>New seed and traits.</t>
+          <t>Seeded traits from species mean ± variation.</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>FR-403</t>
+          <t>FR-401</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>SCR-13-03</t>
+          <t>SCR-13-02</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>API-IND-003</t>
+          <t>API-IND-002</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>set_lock</t>
+          <t>reroll_agent</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -14665,7 +15062,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Lock personality.</t>
+          <t>New seed and traits.</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -14675,19 +15072,19 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>SCR-13-04</t>
+          <t>SCR-13-03</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>API-IND-004</t>
+          <t>API-IND-003</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>set_trait</t>
+          <t>set_lock</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -14702,29 +15099,29 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Edit one trait of one animal.</t>
+          <t>Lock personality.</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>FR-402</t>
+          <t>FR-403</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>SCR-13-09</t>
+          <t>SCR-13-04</t>
         </is>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>API-IND-005</t>
+          <t>API-IND-004</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>apply_preset_agent</t>
+          <t>set_trait</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -14739,7 +15136,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Apply preset to one animal.</t>
+          <t>Edit one trait of one animal.</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -14749,19 +15146,19 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>SCR-13-07</t>
+          <t>SCR-13-09</t>
         </is>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>API-IND-006</t>
+          <t>API-IND-005</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>edit_quirks</t>
+          <t>apply_preset_agent</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -14776,140 +15173,140 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Add/remove quirks.</t>
+          <t>Apply preset to one animal.</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>FR-404</t>
+          <t>FR-402</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>SCR-13-10</t>
+          <t>SCR-13-07</t>
         </is>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
+          <t>API-IND-006</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>edit_quirks</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>noetic_editor::individuals</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Command (undoable)</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Add/remove quirks.</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>FR-404</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>SCR-13-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
           <t>API-IND-007</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>set_forgetting</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::individuals</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>Enable memory decay.</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>FR-405</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
+      <c r="G100" s="4" t="inlineStr">
         <is>
           <t>SCR-13-11</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="29" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
+    <row r="101" ht="29" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>API-IND-008</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>run_sandbox</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>noetic_core::sandbox</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>Same stimulus, different reactions — isolated run.</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>FR-406</t>
         </is>
       </c>
-      <c r="G100" s="4" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>SCR-14-01, SCR-14-02, SCR-14-03, SCR-14-04, SCR-14-05, SCR-14-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>API-IND-009</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>rename_agent</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor::individuals</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>Command (undoable)</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Rename animal.</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>FR-401</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>SCR-13-01</t>
         </is>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>API-IND-010</t>
+          <t>API-IND-009</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>radar_view</t>
+          <t>rename_agent</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -14919,34 +15316,34 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Builder</t>
+          <t>Command (undoable)</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Radar chart: agent vs species mean.</t>
+          <t>Rename animal.</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>FR-402</t>
+          <t>FR-401</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>SCR-13-06</t>
+          <t>SCR-13-01</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>API-IND-011</t>
+          <t>API-IND-010</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>learned_view</t>
+          <t>radar_view</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -14961,66 +15358,66 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>List memories with strength bars.</t>
+          <t>Radar chart: agent vs species mean.</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>FR-405</t>
+          <t>FR-402</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>SCR-13-11</t>
+          <t>SCR-13-06</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>API-IO-001</t>
+          <t>API-IND-011</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>export_species</t>
+          <t>learned_view</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::io</t>
+          <t>noetic_editor::individuals</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>fn</t>
+          <t>Builder</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Serialize FMT-01.</t>
+          <t>List memories with strength bars.</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>FR-601</t>
+          <t>FR-405</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>SCR-09-03, DLG-02-01, DLG-02-02</t>
+          <t>SCR-13-11</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>API-IO-002</t>
+          <t>API-IO-001</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>parse_species</t>
+          <t>export_species</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -15035,29 +15432,29 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Parse RON with line/column errors.</t>
+          <t>Serialize FMT-01.</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>FR-602, SEC-02</t>
+          <t>FR-601</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>DLG-03-03</t>
+          <t>SCR-09-03, DLG-02-01, DLG-02-02</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>API-IO-003</t>
+          <t>API-IO-002</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>validate_species</t>
+          <t>parse_species</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -15072,12 +15469,12 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Rules V-01…V-05.</t>
+          <t>Parse RON with line/column errors.</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>FR-602</t>
+          <t>FR-602, SEC-02</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -15089,123 +15486,123 @@
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
+          <t>API-IO-003</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>validate_species</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::io</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Rules V-01…V-05.</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>FR-602</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>DLG-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
           <t>API-IO-004</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>migrate</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>noetic_core::io::migrate</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
         <is>
           <t>Upgrade older schema versions step by step.</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr">
+      <c r="G108" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="29" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+    <row r="109" ht="29" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>API-IO-005</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>import_species</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::io</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>Command (undoable)</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>Import from file or pasted text.</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>FR-602</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr">
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>SCR-02-04, DLG-03-01, DLG-03-02, DLG-03-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>API-IO-006</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>copy_to_clipboard</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor::io</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>fn</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Copy text (desktop clipboard).</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>FR-601</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>DLG-02-03, DLG-05-04</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>API-IO-007</t>
+          <t>API-IO-006</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>save_file_dialog</t>
+          <t>copy_to_clipboard</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -15220,7 +15617,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Native save dialog (rfd).</t>
+          <t>Copy text (desktop clipboard).</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -15230,187 +15627,187 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>DLG-02-03</t>
+          <t>DLG-02-03, DLG-05-04</t>
         </is>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
+          <t>API-IO-007</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>save_file_dialog</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>noetic_editor::io</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Native save dialog (rfd).</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>FR-601</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLG-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
           <t>API-NET-001</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>remote_connect</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::remote</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>Connect to a running game (BRP).</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="F112" s="4" t="inlineStr">
         <is>
           <t>FR-605</t>
         </is>
       </c>
-      <c r="G111" s="4" t="inlineStr">
+      <c r="G112" s="4" t="inlineStr">
         <is>
           <t>SCR-01-10, DLG-04-01, DLG-04-02</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="29" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="113" ht="29" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>API-NET-002</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>remote_poll_system</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::remote</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>System (Update, async task)</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Poll agent list/state every 250 ms.</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>FR-605</t>
         </is>
       </c>
-      <c r="G112" s="4" t="inlineStr">
+      <c r="G113" s="4" t="inlineStr">
         <is>
           <t>DLG-04-02</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>API-NET-003</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>remote_disconnect</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>noetic_editor::remote</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>Stop polling.</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>FR-605</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr">
+      <c r="G114" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="29" customHeight="1">
-      <c r="A114" s="4" t="inlineStr">
+    <row r="115" ht="29" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>API-COR-001</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>tick</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>noetic_core::sim</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="E115" s="4" t="inlineStr">
         <is>
           <t>One SimWorld step for the editor: think_agent, act_agent and apply_effect in PRC order.</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>PRC-01…17</t>
-        </is>
-      </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>API-COR-002</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>update_needs</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>noetic_core::agent::needs</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>fn</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>Needs rise per hour; active need drops.</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>FR-501</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -15422,17 +15819,17 @@
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>API-COR-003</t>
+          <t>API-COR-002</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>perceive</t>
+          <t>update_needs</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::perception</t>
+          <t>noetic_core::agent::needs</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -15442,34 +15839,34 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Vision, hearing, smell detection.</t>
+          <t>Needs rise per hour; active need drops.</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>FR-502</t>
+          <t>FR-501</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>SCR-06-09</t>
+          <t>(internal)</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>API-COR-004</t>
+          <t>API-COR-003</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>update_memory</t>
+          <t>perceive</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::agent::memory</t>
+          <t>noetic_core::perception</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -15479,34 +15876,34 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Habituation, scare spots, water/shelter/marks.</t>
+          <t>Vision, hearing, smell detection.</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>FR-405</t>
+          <t>FR-502</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>(internal)</t>
+          <t>SCR-06-09</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>API-COR-005</t>
+          <t>API-COR-004</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>update_fear</t>
+          <t>update_memory</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::emotion</t>
+          <t>noetic_core::agent::memory</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -15516,12 +15913,12 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Fear gain/decay by personality.</t>
+          <t>Habituation, scare spots, water/shelter/marks.</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>FR-503</t>
+          <t>FR-405</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -15533,17 +15930,17 @@
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>API-COR-006</t>
+          <t>API-COR-005</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>threat_branch</t>
+          <t>update_fear</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::reaction</t>
+          <t>noetic_core::emotion</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -15553,12 +15950,12 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Start/continue reactions.</t>
+          <t>Fear gain/decay by personality.</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>FR-105, FR-503</t>
+          <t>FR-503</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -15570,69 +15967,69 @@
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
+          <t>API-COR-006</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>threat_branch</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::reaction</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Start/continue reactions.</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>FR-105, FR-503</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
           <t>API-COR-007</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>weighted_pick</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>noetic_core::rng</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>fn (pure)</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>Pick by integer weights.</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>FR-105</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="29" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>API-COR-008</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>propagate_alarm</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>noetic_core::social</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>fn</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>Raises the fear of one neighbour for a queued alarm (any species).</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>FR-504</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -15644,128 +16041,128 @@
     <row r="122" ht="29" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
+          <t>API-COR-008</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>propagate_alarm</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::social</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Raises the fear of one neighbour for a queued alarm (any species).</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>FR-504</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="29" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
           <t>API-COR-009</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>choose_activity</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>noetic_core::utility</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>Utility choice.</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
         <is>
           <t>FR-109, FR-110, FR-510</t>
         </is>
       </c>
-      <c r="G122" s="4" t="inlineStr">
+      <c r="G123" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>API-COR-010</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>curve_eval</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>noetic_core::utility</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>fn (pure)</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>Utility curves.</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>FR-109</t>
-        </is>
-      </c>
-      <c r="G123" s="4" t="inlineStr">
-        <is>
-          <t>SCR-03-14</t>
         </is>
       </c>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>API-COR-011</t>
+          <t>API-COR-010</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>run_step</t>
+          <t>curve_eval</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::steps</t>
+          <t>noetic_core::utility</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>fn</t>
+          <t>fn (pure)</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Execute current step.</t>
+          <t>Utility curves.</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>FR-108</t>
+          <t>FR-109</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>(internal)</t>
+          <t>SCR-03-14</t>
         </is>
       </c>
     </row>
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>API-COR-012</t>
+          <t>API-COR-011</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>follow_group</t>
+          <t>run_step</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::social</t>
+          <t>noetic_core::steps</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -15775,12 +16172,12 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Members keep distance to leader.</t>
+          <t>Execute current step.</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>FR-505</t>
+          <t>FR-108</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -15792,17 +16189,17 @@
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>API-COR-013</t>
+          <t>API-COR-012</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>follow_group</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::conflict</t>
+          <t>noetic_core::social</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -15812,12 +16209,12 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Same-species fight resolution.</t>
+          <t>Members keep distance to leader.</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>FR-507</t>
+          <t>FR-505</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -15829,12 +16226,12 @@
     <row r="127" ht="16" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>API-COR-014</t>
+          <t>API-COR-013</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>apply_damage / heal</t>
+          <t>fight</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -15849,12 +16246,12 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Health, pain→fear, limp, death.</t>
+          <t>Same-species fight resolution.</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>FR-508</t>
+          <t>FR-507</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -15866,106 +16263,106 @@
     <row r="128" ht="16" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
+          <t>API-COR-014</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>apply_damage / heal</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::conflict</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Health, pain→fear, limp, death.</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>FR-508</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
           <t>API-COR-015</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>scent_marks</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C129" s="4" t="inlineStr">
         <is>
           <t>noetic_core::territory</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="E129" s="4" t="inlineStr">
         <is>
           <t>Leave and decay marks.</t>
         </is>
       </c>
-      <c r="F128" s="4" t="inlineStr">
+      <c r="F129" s="4" t="inlineStr">
         <is>
           <t>FR-506</t>
         </is>
       </c>
-      <c r="G128" s="4" t="inlineStr">
+      <c r="G129" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="29" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
+    <row r="130" ht="29" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>API-COR-016</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>locomotion</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>noetic_core::locomotion</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>Movement intent (target, gait, speed, gaze); never moves the agent.</t>
         </is>
       </c>
-      <c r="F129" s="4" t="inlineStr">
+      <c r="F130" s="4" t="inlineStr">
         <is>
           <t>FR-509</t>
-        </is>
-      </c>
-      <c r="G129" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>API-COR-017</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>Rng</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>noetic_core::rng</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>Deterministic PRNG per agent.</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>NFR-01</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -15977,32 +16374,32 @@
     <row r="131" ht="16" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>API-COR-018</t>
+          <t>API-COR-017</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>routine_factor</t>
+          <t>Rng</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>noetic_core::utility</t>
+          <t>noetic_core::rng</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>fn (pure)</t>
+          <t>type</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Preference to rest outside active hours.</t>
+          <t>Deterministic PRNG per agent.</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>FR-510</t>
+          <t>NFR-01</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -16014,12 +16411,12 @@
     <row r="132" ht="16" customHeight="1">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>API-COR-019</t>
+          <t>API-COR-018</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>active_windows</t>
+          <t>routine_factor</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -16034,123 +16431,123 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Routine windows for the day strip.</t>
+          <t>Preference to rest outside active hours.</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>FR-204</t>
+          <t>FR-510</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>SCR-05-18</t>
+          <t>(internal)</t>
         </is>
       </c>
     </row>
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
+          <t>API-COR-019</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>active_windows</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::utility</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>fn (pure)</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Routine windows for the day strip.</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>FR-204</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>SCR-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
           <t>API-COR-020</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>think_agent</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>noetic_core::sim</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="E134" s="4" t="inlineStr">
         <is>
           <t>Think stages for one agent (PRC-03…10).</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="F134" s="4" t="inlineStr">
         <is>
           <t>NFR-02, NFR-03</t>
         </is>
       </c>
-      <c r="G133" s="4" t="inlineStr">
+      <c r="G134" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="29" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
+    <row r="135" ht="29" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>API-COR-021</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>act_agent</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>noetic_core::sim</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
+      <c r="E135" s="4" t="inlineStr">
         <is>
           <t>Act stages for one agent (PRC-11…15); returns its Movement.</t>
         </is>
       </c>
-      <c r="F134" s="4" t="inlineStr">
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>NFR-02</t>
-        </is>
-      </c>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>API-COR-022</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>apply_effect</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>noetic_core::sim</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>fn</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Apply one queued Effect to one agent (PRC-17).</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>FR-504, FR-507</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -16162,12 +16559,12 @@
     <row r="136" ht="16" customHeight="1">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>API-COR-023</t>
+          <t>API-COR-022</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>think_due</t>
+          <t>apply_effect</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -16177,17 +16574,17 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>fn (pure)</t>
+          <t>fn</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Whether an agent thinks on this fixed step.</t>
+          <t>Apply one queued Effect to one agent (PRC-17).</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>FR-504, FR-507</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -16199,32 +16596,32 @@
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>API-RT-001</t>
+          <t>API-COR-023</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>NoeticPlugin::build</t>
+          <t>think_due</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>noetic::plugin</t>
+          <t>noetic_core::sim</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Plugin</t>
+          <t>fn (pure)</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Register assets, components, systems, events.</t>
+          <t>Whether an agent thinks on this fixed step.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>FR-603</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -16236,27 +16633,27 @@
     <row r="138" ht="16" customHeight="1">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>API-RT-002</t>
+          <t>API-RT-001</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>SpeciesLoader</t>
+          <t>NoeticPlugin::build</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>noetic::asset</t>
+          <t>noetic::plugin</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>AssetLoader</t>
+          <t>Plugin</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Load FMT-01 as asset.</t>
+          <t>Register assets, components, systems, events.</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -16273,69 +16670,69 @@
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
+          <t>API-RT-002</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>SpeciesLoader</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>noetic::asset</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>AssetLoader</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Load FMT-01 as asset.</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>FR-603</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
           <t>API-RT-003</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>hot_reload_system</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>noetic::asset</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>Swap brain on asset change.</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>PRC-23</t>
-        </is>
-      </c>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="29" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>API-RT-004</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>sync_world_system</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>noetic::sync</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>System (NoeticSet::Sync)</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>Read game components into the core world view.</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>FR-604</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -16347,32 +16744,32 @@
     <row r="141" ht="29" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>API-RT-005</t>
+          <t>API-RT-004</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>think_system</t>
+          <t>sync_world_system</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>noetic::think</t>
+          <t>noetic::sync</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>System (NoeticSet::Think)</t>
+          <t>System (NoeticSet::Sync)</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Run think_agent for the agents due this step.</t>
+          <t>Read game components into the core world view.</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>FR-604</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -16384,180 +16781,180 @@
     <row r="142" ht="29" customHeight="1">
       <c r="A142" s="4" t="inlineStr">
         <is>
+          <t>API-RT-005</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>think_system</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>noetic::think</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>System (NoeticSet::Think)</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Run think_agent for the agents due this step.</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>NFR-04</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="29" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
           <t>API-RT-006</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>anim_event_system</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>noetic::anim</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr">
         <is>
           <t>System (NoeticSet::Events)</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
+      <c r="E143" s="4" t="inlineStr">
         <is>
           <t>Emit animation events for the game.</t>
         </is>
       </c>
-      <c r="F142" s="4" t="inlineStr">
+      <c r="F143" s="4" t="inlineStr">
         <is>
           <t>IF-03</t>
         </is>
       </c>
-      <c r="G142" s="4" t="inlineStr">
+      <c r="G143" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>API-RT-007</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>brp_methods</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>noetic::debug</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>BRP handlers</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>Remote debug read-only methods (feature debug).</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr">
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>IF-02, SEC-01</t>
         </is>
       </c>
-      <c r="G143" s="4" t="inlineStr">
+      <c r="G144" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="29" customHeight="1">
-      <c r="A144" s="4" t="inlineStr">
+    <row r="145" ht="29" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>API-RT-008</t>
         </is>
       </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>MoveIntent</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>noetic::nav</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D145" s="4" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
+      <c r="E145" s="4" t="inlineStr">
         <is>
           <t>Movement intent the game reads to move the animal; MoveFailed comes back.</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="F145" s="4" t="inlineStr">
         <is>
           <t>IF-05</t>
         </is>
       </c>
-      <c r="G144" s="4" t="inlineStr">
+      <c r="G145" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>API-RT-009</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>extension_registry</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
         <is>
           <t>noetic_core::ext</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr">
+      <c r="D146" s="4" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>Register custom nodes from Rust.</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>FR-606</t>
-        </is>
-      </c>
-      <c r="G145" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="29" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>API-RT-010</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>act_system</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>noetic::think</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>System (NoeticSet::Act)</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>Run act_agent for every agent; write MoveIntent.</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>FR-509</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -16569,35 +16966,72 @@
     <row r="147" ht="29" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
         <is>
+          <t>API-RT-010</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>act_system</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>noetic::think</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>System (NoeticSet::Act)</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Run act_agent for every agent; write MoveIntent.</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>FR-509</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>(internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="29" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
           <t>API-RT-011</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>apply_effects_system</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>noetic::think</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr">
         <is>
           <t>System (NoeticSet::Apply)</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>Apply every queued Effect in order.</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>FR-504, FR-507</t>
         </is>
       </c>
-      <c r="G147" s="4" t="inlineStr">
+      <c r="G148" s="4" t="inlineStr">
         <is>
           <t>(internal)</t>
         </is>
@@ -16619,7 +17053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16646,7 +17080,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>All 195 items of the External Design</t>
+          <t xml:space="preserve">All 196 items of the External Design</t>
         </is>
       </c>
     </row>
@@ -17751,12 +18185,12 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>API-BRN-013, API-PRJ-003</t>
+          <t xml:space="preserve">API-BRN-026</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>update_activity, duplicate_item</t>
+          <t xml:space="preserve">create_activity</t>
         </is>
       </c>
     </row>
@@ -18819,7 +19253,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Need that drives the score (hunger, thirst, fatigue, fear, boredom, urge to mark/fight/sing…).</t>
+          <t xml:space="preserve">Need that drives the score (hunger, thirst, fatigue, fear, safety, company, curiosity, boredom, urge to mark/fight/sing…).</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -20521,7 +20955,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Drag items to move; handles resize.</t>
+          <t xml:space="preserve">Drag items or river points to move; handles resize.</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -23380,57 +23814,61 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Copies to clipboard (desktop: save dialog).</t>
+          <t xml:space="preserve">Copies the file to the clipboard.</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>API-IO-006, API-IO-007</t>
+          <t xml:space="preserve">API-IO-006</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>copy_to_clipboard, save_file_dialog</t>
+          <t xml:space="preserve">copy_to_clipboard</t>
         </is>
       </c>
     </row>
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>DLG-03-01</t>
+          <t xml:space="preserve">DLG-02-04</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>DLG-03 Import .ron dialog</t>
+          <t xml:space="preserve">DLG-02 Export .ron dialog</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>filRon</t>
+          <t xml:space="preserve">btnSaveRon</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr"/>
+          <t xml:space="preserve">Save…</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opens a save dialog for the file.</t>
+        </is>
+      </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>API-IO-005</t>
+          <t xml:space="preserve">API-IO-007</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>import_species</t>
+          <t xml:space="preserve">save_file_dialog</t>
         </is>
       </c>
     </row>
     <row r="189" ht="16" customHeight="1">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>DLG-03-02</t>
+          <t>DLG-03-01</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -23440,12 +23878,12 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>txtRonPaste</t>
+          <t>filRon</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Pasted text</t>
+          <t>File</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr"/>
@@ -23460,187 +23898,187 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="29" customHeight="1">
+    <row r="190" ht="16" customHeight="1">
       <c r="A190" s="4" t="inlineStr">
         <is>
+          <t>DLG-03-02</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>DLG-03 Import .ron dialog</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>txtRonPaste</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>Pasted text</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr"/>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>API-IO-005</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>import_species</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="29" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
           <t>DLG-03-03</t>
         </is>
       </c>
-      <c r="B190" s="4" t="inlineStr">
+      <c r="B191" s="4" t="inlineStr">
         <is>
           <t>DLG-03 Import .ron dialog</t>
         </is>
       </c>
-      <c r="C190" s="4" t="inlineStr">
+      <c r="C191" s="4" t="inlineStr">
         <is>
           <t>btnDoImport</t>
         </is>
       </c>
-      <c r="D190" s="4" t="inlineStr">
+      <c r="D191" s="4" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
+      <c r="E191" s="4" t="inlineStr">
         <is>
           <t>Parses and validates; errors shown in the dialog.</t>
         </is>
       </c>
-      <c r="F190" s="4" t="inlineStr">
+      <c r="F191" s="4" t="inlineStr">
         <is>
           <t>API-IO-005, API-IO-002, API-IO-003</t>
         </is>
       </c>
-      <c r="G190" s="4" t="inlineStr">
+      <c r="G191" s="4" t="inlineStr">
         <is>
           <t>import_species, parse_species, validate_species</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="16" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>DLG-04-01</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>DLG-04 Connect to Game dialog</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>txtAddress</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="E191" s="4" t="inlineStr"/>
-      <c r="F191" s="4" t="inlineStr">
-        <is>
-          <t>API-NET-001</t>
-        </is>
-      </c>
-      <c r="G191" s="4" t="inlineStr">
-        <is>
-          <t>remote_connect</t>
         </is>
       </c>
     </row>
     <row r="192" ht="16" customHeight="1">
       <c r="A192" s="4" t="inlineStr">
         <is>
+          <t>DLG-04-01</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>DLG-04 Connect to Game dialog</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>txtAddress</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr"/>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>API-NET-001</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>remote_connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="16" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
           <t>DLG-04-02</t>
         </is>
       </c>
-      <c r="B192" s="4" t="inlineStr">
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t>DLG-04 Connect to Game dialog</t>
         </is>
       </c>
-      <c r="C192" s="4" t="inlineStr">
+      <c r="C193" s="4" t="inlineStr">
         <is>
           <t>btnConnect</t>
         </is>
       </c>
-      <c r="D192" s="4" t="inlineStr">
+      <c r="D193" s="4" t="inlineStr">
         <is>
           <t>Connect</t>
         </is>
       </c>
-      <c r="E192" s="4" t="inlineStr">
+      <c r="E193" s="4" t="inlineStr">
         <is>
           <t>Tries to connect; shows state.</t>
         </is>
       </c>
-      <c r="F192" s="4" t="inlineStr">
+      <c r="F193" s="4" t="inlineStr">
         <is>
           <t>API-NET-001, API-NET-002</t>
         </is>
       </c>
-      <c r="G192" s="4" t="inlineStr">
+      <c r="G193" s="4" t="inlineStr">
         <is>
           <t>remote_connect, remote_poll_system</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="29" customHeight="1">
-      <c r="A193" s="4" t="inlineStr">
+    <row r="194" ht="29" customHeight="1">
+      <c r="A194" s="4" t="inlineStr">
         <is>
           <t>DLG-05-01</t>
         </is>
       </c>
-      <c r="B193" s="4" t="inlineStr">
+      <c r="B194" s="4" t="inlineStr">
         <is>
           <t>DLG-05 Animation List dialog</t>
         </is>
       </c>
-      <c r="C193" s="4" t="inlineStr">
+      <c r="C194" s="4" t="inlineStr">
         <is>
           <t>tblAnimations</t>
         </is>
       </c>
-      <c r="D193" s="4" t="inlineStr">
+      <c r="D194" s="4" t="inlineStr">
         <is>
           <t>Animations</t>
         </is>
       </c>
-      <c r="E193" s="4" t="inlineStr">
+      <c r="E194" s="4" t="inlineStr">
         <is>
           <t>Event, what the animal does, duration, loop, where used, clip.</t>
         </is>
       </c>
-      <c r="F193" s="4" t="inlineStr">
+      <c r="F194" s="4" t="inlineStr">
         <is>
           <t>API-SPC-010</t>
         </is>
       </c>
-      <c r="G193" s="4" t="inlineStr">
+      <c r="G194" s="4" t="inlineStr">
         <is>
           <t>animation_rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="16" customHeight="1">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>DLG-05-02</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>DLG-05 Animation List dialog</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>segFormat</t>
-        </is>
-      </c>
-      <c r="D194" s="4" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="E194" s="4" t="inlineStr"/>
-      <c r="F194" s="4" t="inlineStr">
-        <is>
-          <t>API-SPC-011</t>
-        </is>
-      </c>
-      <c r="G194" s="4" t="inlineStr">
-        <is>
-          <t>format_animation_list</t>
         </is>
       </c>
     </row>
     <row r="195" ht="16" customHeight="1">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>DLG-05-03</t>
+          <t>DLG-05-02</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -23650,12 +24088,12 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>txtSheet</t>
+          <t>segFormat</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Export text</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr"/>
@@ -23673,7 +24111,7 @@
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>DLG-05-04</t>
+          <t>DLG-05-03</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -23683,132 +24121,165 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>btnCopySheet</t>
+          <t>txtSheet</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>Export text</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr"/>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>API-IO-006</t>
+          <t>API-SPC-011</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>copy_to_clipboard</t>
+          <t>format_animation_list</t>
         </is>
       </c>
     </row>
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="4" t="inlineStr">
         <is>
+          <t>DLG-05-04</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>DLG-05 Animation List dialog</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>btnCopySheet</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Copy</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr"/>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>API-IO-006</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>copy_to_clipboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
           <t>DLG-06-01</t>
         </is>
       </c>
-      <c r="B197" s="4" t="inlineStr">
+      <c r="B198" s="4" t="inlineStr">
         <is>
           <t>DLG-06 Quick Guide dialog</t>
         </is>
       </c>
-      <c r="C197" s="4" t="inlineStr">
+      <c r="C198" s="4" t="inlineStr">
         <is>
           <t>dlgGuide</t>
         </is>
       </c>
-      <c r="D197" s="4" t="inlineStr">
+      <c r="D198" s="4" t="inlineStr">
         <is>
           <t>Quick guide</t>
         </is>
       </c>
-      <c r="E197" s="4" t="inlineStr">
+      <c r="E198" s="4" t="inlineStr">
         <is>
           <t>Close: "Got it", × or Esc.</t>
         </is>
       </c>
-      <c r="F197" s="4" t="inlineStr">
+      <c r="F198" s="4" t="inlineStr">
         <is>
           <t>API-APP-003, API-APP-004</t>
         </is>
       </c>
-      <c r="G197" s="4" t="inlineStr">
+      <c r="G198" s="4" t="inlineStr">
         <is>
           <t>open_dialog, close_dialog</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="29" customHeight="1">
-      <c r="A198" s="4" t="inlineStr">
-        <is>
-          <t>POP-01-01</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>POP-01 Tree Context Menu</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>mnuTreeItem</t>
-        </is>
-      </c>
-      <c r="D198" s="4" t="inlineStr">
-        <is>
-          <t>Item menu</t>
-        </is>
-      </c>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>Folder rows show: new item here, rename, delete folder.</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>API-PRJ-011, API-PRJ-002, API-PRJ-003, API-PRJ-004, API-PRJ-005</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="inlineStr">
-        <is>
-          <t>context_menu, rename_item, duplicate_item, move_item, delete_item</t>
         </is>
       </c>
     </row>
     <row r="199" ht="29" customHeight="1">
       <c r="A199" s="4" t="inlineStr">
         <is>
+          <t>POP-01-01</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>POP-01 Tree Context Menu</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>mnuTreeItem</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>Item menu</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>Folder rows show: new item here, rename, delete folder.</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>API-PRJ-011, API-PRJ-002, API-PRJ-003, API-PRJ-004, API-PRJ-005</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>context_menu, rename_item, duplicate_item, move_item, delete_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="29" customHeight="1">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
           <t>POP-02-01</t>
         </is>
       </c>
-      <c r="B199" s="4" t="inlineStr">
+      <c r="B200" s="4" t="inlineStr">
         <is>
           <t>POP-02 Tooltip</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr">
+      <c r="C200" s="4" t="inlineStr">
         <is>
           <t>tipHover</t>
         </is>
       </c>
-      <c r="D199" s="4" t="inlineStr">
+      <c r="D200" s="4" t="inlineStr">
         <is>
           <t>Tooltip</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
+      <c r="E200" s="4" t="inlineStr">
         <is>
           <t>Shown after a short delay; hides on leave.</t>
         </is>
       </c>
-      <c r="F199" s="4" t="inlineStr">
+      <c r="F200" s="4" t="inlineStr">
         <is>
           <t>API-APP-005</t>
         </is>
       </c>
-      <c r="G199" s="4" t="inlineStr">
+      <c r="G200" s="4" t="inlineStr">
         <is>
           <t>tooltip_system</t>
         </is>
@@ -24330,8 +24801,8 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. Ignore when a text input has focus (except Esc).
-2. Space→API-SIM-001, Ctrl+B/I→API-APP-002, Delete→API-BRN-009/API-PRJ-005, F2→API-PRJ-002, Ctrl+Z→API-PRJ-006, Esc→API-APP-004.</t>
+          <t xml:space="preserve">1. Ignore when a text input has focus (except Esc).
+2. Space→API-SIM-001, Ctrl+B/I→API-APP-002, Delete→API-BRN-009 (block), API-BRN-004 (connection) or API-PRJ-005 (tree item), F2→API-PRJ-002, Ctrl+Z→API-PRJ-006, Ctrl+Shift+Z→API-PRJ-007, Esc→API-APP-004 (dialog), closes an open menu or cancels a wire drag (API-BRN-025).</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -24363,7 +24834,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>fn brand_widget() -&gt; impl Bundle</t>
+          <t xml:space="preserve">fn logo_and_brand() -&gt; impl Bundle</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -24618,8 +25089,8 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. Validate mult ∈ {0.5,1,4,16}.
-2. host.speed = mult; ticks per frame = round(mult × frame_dt / FIXED_DT) with cap 64.</t>
+          <t xml:space="preserve">1. Validate mult ∈ {0.5,1,4,16}.
+2. host.speed = mult; sim_host_system adds it to the tick accumulator each fixed step (API-SIM-007).</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -24810,7 +25281,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1. If running: for n ticks call core::sim::tick(&amp;mut host.world, FIXED_DT).
+          <t xml:space="preserve">1. If running: accumulator += speed; while accumulator ≥ 1 (at most 64 times) call core::sim::tick(&amp;mut host.world, FIXED_DT) and subtract 1.
 2. Collect SimEvents for the view (history, toasts).</t>
         </is>
       </c>
@@ -25009,7 +25480,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>NameError::Empty|TooLong|Duplicate → inline error</t>
+          <t xml:space="preserve">NameError::Empty|TooLong|Duplicate → MSG-029 inline</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -25062,7 +25533,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>SCR-02-08, POP-01-01</t>
+          <t xml:space="preserve">POP-01-01</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -25132,7 +25603,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>fn delete_item(p: &amp;mut Project, key: TreeKey) -&gt; UndoToken</t>
+          <t xml:space="preserve">fn delete_item(p: &amp;mut Project, sim: &amp;mut SimHost, key: TreeKey) -&gt; UndoToken</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -25181,7 +25652,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>fn undo(h: &amp;mut History, p: &amp;mut Project, sim: &amp;mut SimHost)</t>
+          <t xml:space="preserve">fn undo(h: &amp;mut History, p: &amp;mut Project, sim: &amp;mut SimHost, token: Option&lt;UndoToken&gt;)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -25196,8 +25667,8 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1. Pop command.
-2. Apply inverse.
+          <t xml:space="preserve">1. With a token: do nothing unless it names the last command (the toast is stale).
+2. Pop command; apply its inverse.
 3. Push to redo stack.</t>
         </is>
       </c>
@@ -25255,64 +25726,65 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEY-12</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>API-PRJ-008</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>save_project</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>fn save_project(p: &amp;Project, sim: &amp;SimWorld, path: &amp;Path) -&gt; Result&lt;(), IoError&gt;</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Copy each agent of sim into individuals (species, name, seed, position, traits, quirks, locked).
+2. Serialize RON (pretty).
+3. Write temp file; fsync; rename.</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IoError → MSG-026; retry on the next change</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
           <t>(internal)</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="29" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>API-PRJ-008</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>save_project</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>fn save_project(p: &amp;Project, path: &amp;Path) -&gt; Result&lt;(), IoError&gt;</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. Serialize RON (pretty).
-2. Write temp file; fsync; rename.</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>IoError → toast + retry next change</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>(internal)</t>
-        </is>
-      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="29" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>API-PRJ-009</t>
@@ -25325,7 +25797,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>fn load_project(path: &amp;Path) -&gt; Result&lt;Project, LoadError&gt;</t>
+          <t xml:space="preserve">fn load_project(path: &amp;Path, sim: &amp;mut SimHost) -&gt; Result&lt;Project, LoadError&gt;</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -25340,13 +25812,14 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1. Read; parse; migrate (API-IO-004).
-2. Rebuild graphs; spawn agents.</t>
+          <t xml:space="preserve">1. Read as ron::Value; migrate (API-IO-004); deserialize into Project.
+2. Rebuild graphs.
+3. Respawn each individual with API-WLD-005 (its seed), then restore name, traits, quirks and locked.</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>LoadError → open default project + message</t>
+          <t xml:space="preserve">LoadError → open default project + MSG-027</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -25421,7 +25894,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>fn open_item_menu(key: TreeKey, pos: Vec2)</t>
+          <t xml:space="preserve">fn context_menu(key: TreeKey, pos: Vec2)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -25456,7 +25929,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="29" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>API-PRJ-012</t>
@@ -25469,7 +25942,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>fn autosave_system(p: Res&lt;Project&gt;, mut t: Local&lt;Debounce&gt;)</t>
+          <t>fn autosave_system(p: Res&lt;Project&gt;, sim: Res&lt;SimHost&gt;, mut t: Local&lt;Debounce&gt;)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -25484,8 +25957,9 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>1. On Project change start 2 s timer.
-2. On expiry call API-PRJ-008.</t>
+          <t>1. On ProjectChanged (EVT-06), including an individual spawned or edited, start 2 s timer.
+2. On expiry call API-PRJ-008.
+3. On AppExit save at once.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4586" uniqueCount="2392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4591" uniqueCount="2394">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -6358,7 +6358,7 @@
 a.needs[Sing]    += (if (5.0..10.0).contains(&amp;hour) || (16.0..19.0).contains(&amp;hour) { 90.0 } else { -50.0 }) * dt_h;
 a.needs[Safety]  += (if near_shelter_or_own_safe_mark(a, view, 6.0) { 10.0 } else { -2.0 }) * dt;   // per second
 a.needs[Company] += (if group_member_within(a, view, 15.0) { -40.0 } else { 20.0 }) * dt_h;     // group species only
-a.needs.clamp_all(0.0, 100.0);                     // an activity lowers its need in run_step (API-COR-011)
+for v in a.needs.values_mut() { *v = v.clamp(0.0, 100.0); }                     // an activity lowers its need in run_step (API-COR-011)
 // driving values for ALG-10, drive(a, sp, need, hour):
 //   Hunger, Thirst, Heat, Sing, Company → the need · Fatigue → need + 55 outside active hours + 35 if limping
 //   Safety → 100 − safety · Fear → 25 + a.fear × 0.8 · Calm → (100 − a.fear) × 0.55
@@ -7525,6 +7525,12 @@
   </si>
   <si>
     <t xml:space="preserve">Rng samples through rand: unit, range and below call it and return the lower end on an empty range, since rand panics there (EP-01); range takes min and max (API-COR-017); weighted_pick is rand's choose_weighted over u32 weights (ALG-07b). A rand upgrade may change the draws of a seed, so the golden test is refreshed with it (NFR-01).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs is an EnumMap&lt;Need, f32&gt; from enum-map, so ALG-02 clamps every value through values_mut instead of a clamp_all of its own.</t>
   </si>
 </sst>
 </file>
@@ -8057,7 +8063,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12347,7 +12353,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12543,6 +12549,20 @@
       </c>
       <c r="D15" s="4" t="s">
         <v>2391</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>2393</v>
       </c>
     </row>
   </sheetData>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4591" uniqueCount="2394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="2405">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">38 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">41 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -7531,6 +7531,39 @@
   </si>
   <si>
     <t xml:space="preserve">Needs is an EnumMap&lt;Need, f32&gt; from enum-map, so ALG-02 clamps every value through values_mut instead of a clamp_all of its own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thirst 0, thirst_per_h 10, 2 game hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thirst 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">appetite 50, hunger_per_h 10, 1 game hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunger 10 (factor 1.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunger 95, rates 10, 10 game hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunger and thirst 100, never more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-003 is written; new UT-039…041 for update_needs (API-COR-002): thirst rises by the rate per game hour, average appetite keeps the species hunger rate, a need never passes 100; 41 unit test cases.</t>
   </si>
 </sst>
 </file>
@@ -8063,7 +8096,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2392</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12353,7 +12386,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12563,6 +12596,20 @@
       </c>
       <c r="D16" s="4" t="s">
         <v>2393</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>2404</v>
       </c>
     </row>
   </sheetData>
@@ -13923,7 +13970,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -14767,6 +14814,69 @@
         <v>2388</v>
       </c>
       <c r="G42" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>2396</v>
+      </c>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>2397</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>2398</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>2402</v>
+      </c>
+      <c r="G45" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="2405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4641" uniqueCount="2419">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">41 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">45 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -7564,6 +7564,48 @@
   </si>
   <si>
     <t xml:space="preserve">UT-003 is written; new UT-039…041 for update_needs (API-COR-002): thirst rises by the rate per game hour, average appetite keeps the species hunger rate, a need never passes 100; 41 unit test cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heat 0, middle of the hot hours (13.5 h), 1 game hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heat 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heat 15, 2 h at night, 1 game hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heat 0, never below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urge to sing 0, middle of the morning (7.5 h) and of the evening (17.5 h) song hours, 0.5 game hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urge to sing 45 at both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urge to sing 100, noon, 1 game hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urge to sing 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New UT-042…045 for update_needs (API-COR-002): heat rises in the hot hours and stops at 0 at night, the urge to sing rises at dawn and dusk and drops at midday; 45 unit test cases.</t>
   </si>
 </sst>
 </file>
@@ -8096,7 +8138,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2403</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12386,7 +12428,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12610,6 +12652,20 @@
       </c>
       <c r="D17" s="4" t="s">
         <v>2404</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>2418</v>
       </c>
     </row>
   </sheetData>
@@ -13970,7 +14026,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -14877,6 +14933,90 @@
         <v>2402</v>
       </c>
       <c r="G45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>2407</v>
+      </c>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>2409</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>2412</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>2413</v>
+      </c>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>2415</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>2416</v>
+      </c>
+      <c r="G49" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4641" uniqueCount="2419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4662" uniqueCount="2430">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">45 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">48 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -7606,6 +7606,39 @@
   </si>
   <si>
     <t xml:space="preserve">New UT-042…045 for update_needs (API-COR-002): heat rises in the hot hours and stops at 0 at night, the urge to sing rises at dawn and dusk and drops at midday; 45 unit test cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nocturnal (20–6) checked at 23 h, 3 h and 12 h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active, active, not active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fatigue 0, energy 45, Diurnal, noon, 1 game hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fatigue rises at the species rate (factor 1.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same animal at 2 h, outside the active hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fatigue rises 1.6 × the species rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New UT-046 for active_windows (a window past midnight) and UT-047…048 for update_needs (fatigue at the species rate in the active hours, 1.6 × outside them); 48 unit test cases.</t>
   </si>
 </sst>
 </file>
@@ -8138,7 +8171,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2417</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12428,7 +12461,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12666,6 +12699,20 @@
       </c>
       <c r="D18" s="4" t="s">
         <v>2418</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>2428</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>2429</v>
       </c>
     </row>
   </sheetData>
@@ -14026,7 +14073,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15017,6 +15064,69 @@
         <v>2416</v>
       </c>
       <c r="G49" s="4"/>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>2420</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>2421</v>
+      </c>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>2423</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>2427</v>
+      </c>
+      <c r="G52" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4662" uniqueCount="2430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4671" uniqueCount="2435">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">48 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">49 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -7639,6 +7639,21 @@
   </si>
   <si>
     <t xml:space="preserve">New UT-046 for active_windows (a window past midnight) and UT-047…048 for update_needs (fatigue at the species rate in the active hours, 1.6 × outside them); 48 unit test cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diurnal: rest and non-rest at noon, rest and non-rest at 2 h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0, 1.0, 1.6, 0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New UT-049 for routine_factor (API-COR-018): each branch of the daily rhythm; 49 unit test cases.</t>
   </si>
 </sst>
 </file>
@@ -8171,7 +8186,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2428</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12461,7 +12476,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12713,6 +12728,20 @@
       </c>
       <c r="D19" s="4" t="s">
         <v>2429</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>2434</v>
       </c>
     </row>
   </sheetData>
@@ -14073,7 +14102,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15127,6 +15156,27 @@
         <v>2427</v>
       </c>
       <c r="G52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>2432</v>
+      </c>
+      <c r="G53" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4671" uniqueCount="2435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4704" uniqueCount="2453">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">49 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">54 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -7654,6 +7654,60 @@
   </si>
   <si>
     <t xml:space="preserve">New UT-049 for routine_factor (API-COR-018): each branch of the daily rhythm; 49 unit test cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunger 70; safety 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunger pulls 70; safety pulls 70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fatigue 40, Diurnal: noon; 2 h; 2 h limping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40; 95; 130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fear felt 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fear pulls 65; calm pulls 27.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curiosity and energy traits 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curiosity pulls 50; boredom pulls 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mark and fight needs 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both pull 0 (no scent marks or fights yet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choose_activity (drive)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New UT-050…054 for the driving values of ALG-10 (drive, inside API-COR-009 choose_activity): a need pulls by its value, safety by its lack, fatigue more off hours and when limping, fear and calm by the fear felt now, curiosity and boredom by the traits, mark and fight not yet; 54 unit test cases.</t>
   </si>
 </sst>
 </file>
@@ -8186,7 +8240,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2433</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12476,7 +12530,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12742,6 +12796,20 @@
       </c>
       <c r="D20" s="4" t="s">
         <v>2434</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>2452</v>
       </c>
     </row>
   </sheetData>
@@ -14102,7 +14170,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15177,6 +15245,111 @@
         <v>2432</v>
       </c>
       <c r="G53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>2450</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>2436</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>2437</v>
+      </c>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>2450</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>2439</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>2440</v>
+      </c>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>2450</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>2442</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>2443</v>
+      </c>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>2450</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>2445</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>2446</v>
+      </c>
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>2450</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>2448</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>2449</v>
+      </c>
+      <c r="G58" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4704" uniqueCount="2453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4731" uniqueCount="2467">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">54 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">58 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -6089,10 +6089,10 @@
 Called by apply_effect for each agent in the alarm radius.</t>
   </si>
   <si>
-    <t xml:space="preserve">fn choose_activity(a: &amp;mut Agent, sp: &amp;Species, hour: f32, out: &amp;mut Outbox) -&gt; (ActivityId, Scores)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG-10 with a.rng; think_agent passes hour = view.hour(); options are looked up in sp.activities; runs only while the state is Choosing.
+    <t xml:space="preserve">fn choose_activity(a: &amp;mut Agent, sp: &amp;Species, hour: f32, out: &amp;mut Outbox) -&gt; Option&lt;(ActivityId, Scores)&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG-10 with a.rng; think_agent passes hour = view.hour(); options are looked up in sp.activities; runs only while the state is Choosing; None when no option is in sp.activities.
 Chose goes to out.events.</t>
   </si>
   <si>
@@ -7708,6 +7708,48 @@
   </si>
   <si>
     <t xml:space="preserve">New UT-050…054 for the driving values of ALG-10 (drive, inside API-COR-009 choose_activity): a need pulls by its value, safety by its lack, fatigue more off hours and when limping, fear and calm by the fear felt now, curiosity and boredom by the traits, mark and fight not yet; 54 unit test cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunger 80, thirst 20; options eat and drink, linear, no noise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eat, with both scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two activities with the same score, options in reverse order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the name first in alphabetical order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no options; an option missing from sp.activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None, no panic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same agent and seed twice, noise 0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same choice and scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API-COR-009 choose_activity returns Option&lt;(ActivityId, Scores)&gt;: None when no option is in sp.activities, instead of an empty name; new UT-055…058 (highest wins, tie to the first name, nothing to choose, same seed same scores); 58 unit test cases.</t>
   </si>
 </sst>
 </file>
@@ -8240,7 +8282,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2451</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12530,7 +12572,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12810,6 +12852,20 @@
       </c>
       <c r="D21" s="4" t="s">
         <v>2452</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>2466</v>
       </c>
     </row>
   </sheetData>
@@ -14170,7 +14226,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15350,6 +15406,90 @@
         <v>2449</v>
       </c>
       <c r="G58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>2454</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>2455</v>
+      </c>
+      <c r="G59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>2457</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>2461</v>
+      </c>
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>2464</v>
+      </c>
+      <c r="G62" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4731" uniqueCount="2467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4752" uniqueCount="2478">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">58 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">61 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -6119,7 +6119,7 @@
   <si>
     <t xml:space="preserve">1. On start: duration = a.rng.range(min,max); SimEvent::Anim to out.events.
 2. Move steps: target from memory or perception; fail if none or on MoveFailed → choose again.
-3. Act steps: lower need while running.
+3. Act steps lower their need while running, per second: Eat hunger 14, Drink thirst 20, Rest fatigue 9, Wallow heat 14, Sing urge to sing 20 (from the prototype); other steps lower none. Checks come first, so a step that fails changes nothing.
 4. Done when time over or target reached.</t>
   </si>
   <si>
@@ -7750,6 +7750,39 @@
   </si>
   <si>
     <t xml:space="preserve">API-COR-009 choose_activity returns Option&lt;(ActivityId, Scores)&gt;: None when no option is in sp.activities, instead of an empty name; new UT-055…058 (highest wins, tie to the first name, nothing to choose, same seed same scores); 58 unit test cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunger 50, Eat step of 3 s, run 1 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunger 36 (−14 per s), Running</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same step run twice for 2 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running, then Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a GoTo step; an Eat step while the animal is choosing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed, the animal unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API-COR-011 run_step: the steps that lower a need and how fast (Eat, Drink, Rest, Wallow, Sing, from the prototype); it checks before it changes, so a failure leaves the animal unchanged; new UT-059…061; 61 unit test cases.</t>
   </si>
 </sst>
 </file>
@@ -8282,7 +8315,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2465</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12572,7 +12605,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12866,6 +12899,20 @@
       </c>
       <c r="D22" s="4" t="s">
         <v>2466</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>2477</v>
       </c>
     </row>
   </sheetData>
@@ -14226,7 +14273,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15490,6 +15537,69 @@
         <v>2464</v>
       </c>
       <c r="G62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>2468</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>2469</v>
+      </c>
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>2471</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>2472</v>
+      </c>
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>2474</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>2475</v>
+      </c>
+      <c r="G65" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4752" uniqueCount="2478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4773" uniqueCount="2490">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">61 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">64 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -6117,7 +6117,7 @@
     <t xml:space="preserve">Running|Done|Failed</t>
   </si>
   <si>
-    <t xml:space="preserve">1. On start: duration = a.rng.range(min,max); SimEvent::Anim to out.events.
+    <t xml:space="preserve">1. On entering a step (enter_step): duration = a.rng.range(min, max); SimEvent::Anim to out.events; past the last step the activity ends and the agent is Choosing. do_activity runs the current step: Done enters the next, Failed goes back to Choosing.
 2. Move steps: target from memory or perception; fail if none or on MoveFailed → choose again.
 3. Act steps lower their need while running, per second: Eat hunger 14, Drink thirst 20, Rest fatigue 9, Wallow heat 14, Sing urge to sing 20 (from the prototype); other steps lower none. Checks come first, so a step that fails changes nothing.
 4. Done when time over or target reached.</t>
@@ -7783,6 +7783,42 @@
   </si>
   <si>
     <t xml:space="preserve">API-COR-011 run_step: the steps that lower a need and how fast (Eat, Drink, Rest, Wallow, Sing, from the prototype); it checks before it changes, so a failure leaves the animal unchanged; new UT-059…061; 61 unit test cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enter step 0 of a two-step activity; enter step 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in step 0 with its time within secs; choosing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a two-step activity run with dt longer than each step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">step 0, then step 1, then choosing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">an activity whose first step is GoTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">back to choosing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API-COR-011: the step's time is drawn when the animal enters it (enter_step), and do_activity runs the current step for PRC-11, moving to the next on Done and back to choosing on Failed; new UT-062…064; 64 unit test cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_step (enter_step, do_activity)</t>
   </si>
 </sst>
 </file>
@@ -8315,7 +8351,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2476</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12605,7 +12641,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12913,6 +12949,20 @@
       </c>
       <c r="D23" s="4" t="s">
         <v>2477</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>2488</v>
       </c>
     </row>
   </sheetData>
@@ -14273,7 +14323,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15600,6 +15650,69 @@
         <v>2475</v>
       </c>
       <c r="G65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>2479</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>2480</v>
+      </c>
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>2482</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>2483</v>
+      </c>
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>2485</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G68" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4773" uniqueCount="2490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="2495">
   <si>
     <t xml:space="preserve">Noetic — Detailed Design</t>
   </si>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">8 Unit Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">64 unit test cases (normal, boundary, abnormal)</t>
+    <t xml:space="preserve">65 unit test cases (normal, boundary, abnormal)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Conventions</t>
@@ -7819,6 +7819,21 @@
   </si>
   <si>
     <t xml:space="preserve">run_step (enter_step, do_activity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fatigue 0, in a Rest step at 2 h, 1 game hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fatigue still 0 (no rise while resting)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG-02 `resting` is the animal in an activity whose current step is Rest (is_resting); new UT-065 for update_needs; 65 unit test cases.</t>
   </si>
 </sst>
 </file>
@@ -8351,7 +8366,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2487</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12641,7 +12656,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12963,6 +12978,20 @@
       </c>
       <c r="D24" s="4" t="s">
         <v>2488</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>2494</v>
       </c>
     </row>
   </sheetData>
@@ -14323,7 +14352,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15713,6 +15742,27 @@
         <v>2486</v>
       </c>
       <c r="G68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>2492</v>
+      </c>
+      <c r="G69" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -8365,16 +8365,20 @@
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>2493</v>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.23</t>
+        </is>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>2390</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12656,7 +12660,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -12992,6 +12996,28 @@
       </c>
       <c r="D25" s="4" t="s">
         <v>2494</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.23</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-001 tick: the clock moves on and wraps at 24 h, then every animal thinks and acts in id order; an animal whose species is missing stays idle (NFR-12). Until think_due, SimEvent and Effect exist, every animal thinks on every step and tick returns nothing; new UT-066…068; 68 unit test cases.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -14352,7 +14378,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15763,6 +15789,105 @@
         <v>2492</v>
       </c>
       <c r="G69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-066</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-001</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tick</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clock at 23.5 h, one game hour</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clock at 0.5 h (wraps past midnight)</t>
+        </is>
+      </c>
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-067</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-001</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tick</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an animal of a species not in the world, beside one of a known species</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">that animal unchanged, no panic; the other thirstier</t>
+        </is>
+      </c>
+      <c r="G71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-068</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-001</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tick</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">secs_per_game_hour 0, one step</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clock and needs unchanged</t>
+        </is>
+      </c>
+      <c r="G72" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16012,8 +16137,10 @@
       <c r="B22" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>82</v>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68 unit test cases (normal, boundary, abnormal)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.23</t>
+          <t xml:space="preserve">0.24</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -13017,6 +13017,28 @@
       <c r="D26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">API-COR-001 tick: the clock moves on and wraps at 24 h, then every animal thinks and acts in id order; an animal whose species is missing stays idle (NFR-12). Until think_due, SimEvent and Effect exist, every animal thinks on every step and tick returns nothing; new UT-066…068; 68 unit test cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.24</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-011 run_step lowers a need down to 0 and never below it; it went negative while the animal rested until the next update_needs clamped it. New UT-069; 69 unit test cases.</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14400,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15888,6 +15910,39 @@
         </is>
       </c>
       <c r="G72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-069</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-011</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run_step</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hunger 50, Eat step run long enough to take off 100</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hunger 0, never below</t>
+        </is>
+      </c>
+      <c r="G73" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16139,7 +16194,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">68 unit test cases (normal, boundary, abnormal)</t>
+          <t xml:space="preserve">69 unit test cases (normal, boundary, abnormal)</t>
         </is>
       </c>
     </row>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.24</t>
+          <t xml:space="preserve">0.25</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -13039,6 +13039,28 @@
       <c r="D27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">API-COR-011 run_step lowers a need down to 0 and never below it; it went negative while the animal rested until the next update_needs clamped it. New UT-069; 69 unit test cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.25</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-025 is written (noetic_core/tests/golden.rs): the default world is four diurnal rabbits that graze, drink and rest, seeds 42…45, from 6 h, 1000 ticks of 0.5 s; the state hash is FNV-1a 64 over the world printed with Debug, since DefaultHasher may change between Rust releases. M1 done.</t>
         </is>
       </c>
     </row>

--- a/docs/05_detailed_design.xlsx
+++ b/docs/05_detailed_design.xlsx
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.25</t>
+          <t xml:space="preserve">0.26</t>
         </is>
       </c>
     </row>
@@ -11359,11 +11359,19 @@
       <c r="E5" s="4" t="s">
         <v>1952</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>1953</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>1616</v>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Clock (PRC-01): advances by game_hours (API-COR-020 step 3) and wraps at 24 h.
+2. Every agent in id order: think_agent (API-COR-020) where think_due (API-COR-023), with dt = THINK_DT; then every agent in id order: act_agent (API-COR-021), with dt. All think before any acts, as the Think and Act sets of the game (NFR-02); the simple mover applies each Movement.
+3. Effects sorted by (source, seq) → apply_effect (API-COR-022); marks stored.
+4. World-level marks decay.
+5. Return events.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dt negative, NaN or infinite → counts as 0. An agent whose species is missing → stays idle (NFR-12).</t>
+        </is>
       </c>
       <c r="H5" s="4" t="s">
         <v>141</v>
@@ -11614,11 +11622,15 @@
       <c r="C14" s="4" t="s">
         <v>1974</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>1975</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>1976</v>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x ≥ 0; below 0 counts as 0, fatigue can pass 1</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0–1 for x in 0–1; Linear and Accelerating follow x past 1</t>
+        </is>
       </c>
       <c r="F14" s="4" t="s">
         <v>1977</v>
@@ -11649,8 +11661,13 @@
       <c r="E15" s="4" t="s">
         <v>1980</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>1981</v>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On entering a step (enter_step): duration = a.rng.range(min, max); SimEvent::Anim to out.events; past the last step the activity ends and the agent is Choosing. do_activity runs the current step: Done enters the next, Failed goes back to Choosing.
+2. Move steps: target from memory or perception; fail if none or on MoveFailed → choose again.
+3. Act steps lower their need while running, per second, for the part of dt the step still had (min(dt, time left)) and never below 0: Eat hunger 14, Drink thirst 20, Rest fatigue 9, Wallow heat 14, Sing urge to sing 20 (from the prototype); other steps lower none. Checks come first, so a step that fails changes nothing.
+4. Done when time over or target reached.</t>
+        </is>
       </c>
       <c r="G15" s="4" t="s">
         <v>1616</v>
@@ -11823,8 +11840,12 @@
       <c r="E21" s="4" t="s">
         <v>1616</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>1993</v>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. A live agent's Pcg32 is seeded from agent seed ⊕ species hash; the sandbox reseeds its copy with seed ^ 0x5EED (ALG-12) and personality uses its own Rng::seed(seed) (ALG-09).
+2. No global RNG anywhere in core.
+3. range returns min when the range is empty or not finite, and below(0) returns 0, since rand panics there (EP-01).</t>
+        </is>
       </c>
       <c r="G21" s="4" t="s">
         <v>1616</v>
@@ -11852,8 +11873,11 @@
       <c r="E22" s="4" t="s">
         <v>1616</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>1995</v>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Active windows: Diurnal 6–19, Crepuscular 5–9 &amp; 17–21, Nocturnal 20–6, MorningAfternoon 6–10 &amp; 15–19. A window is [start, end): 19.0 is outside Diurnal.
+2. Inside 1.0; outside 0.35 for non-rest, 1.6 for rest.</t>
+        </is>
       </c>
       <c r="G22" s="4" t="s">
         <v>1616</v>
@@ -11910,8 +11934,13 @@
       <c r="E24" s="4" t="s">
         <v>1616</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>2000</v>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Skip if Dead (PRC-02).
+2. In this order: heal, update_needs, perceive, update_memory, update_fear, threat_branch, choose_activity (PRC-03…10); once it chooses, the agent enters step 0 of that activity (enter_step).
+3. dt_h = game_hours(view, dt) = dt / view.secs_per_game_hour(), 0 when that is 0 (game time stands still); hour = view.hour(), forget = view.forget(); choose_activity runs only while Choosing.
+4. Writes only a; effects for other agents and SimEvents go to out.</t>
+        </is>
       </c>
       <c r="G24" s="4" t="s">
         <v>1616</v>
@@ -12439,8 +12468,10 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>2044</v>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formulas and pseudocode (Rust). Values are initial tuning constants, in the Config section of the file that uses them.</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12660,7 +12691,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -13061,6 +13092,28 @@
       <c r="D28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">UT-025 is written (noetic_core/tests/golden.rs): the default world is four diurnal rabbits that graze, drink and rest, seeds 42…45, from 6 h, 1000 ticks of 0.5 s; the state hash is FNV-1a 64 over the world printed with Debug, since DefaultHasher may change between Rust releases. M1 done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.26</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review of M1. API-COR-011 run_step relieves only for the part of dt the step still had, so the result no longer depends on the step size (golden refreshed); API-COR-001 counts a negative, NaN or infinite dt as 0 and leaves an agent of a missing species idle; API-COR-010 counts x below 0 as 0 (√ of a negative was NaN, and a NaN score won every choice) and lets fatigue pass 1; API-COR-017 range returns min on a non-finite range; API-COR-020 dt_h is 0 when secs_per_game_hour is 0, and the chosen activity is entered at step 0; API-COR-018 windows are [start, end); API-COR-001 runs every think before any act, as the game does (NFR-02). Tuning constants live in the Config section of each file, not in noetic_core::tuning. 6.1 defines SpeciesId. UT-038 is written; UT-041, 058 and 069 now test what their names claim; new UT-070…073; 73 unit test cases. Contents: BRN has 26 APIs.</t>
         </is>
       </c>
     </row>
@@ -13114,8 +13167,36 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="328.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>2076</v>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#[derive(Serialize, Deserialize, Clone, Debug)]
+#[serde(deny_unknown_fields, rename = "NoeticSpecies")]
+pub struct Species {
+    pub schema_version: u32,
+    pub species: String,
+    pub color: Srgb8,                                   // "#RRGGBB"
+    pub locomotion: Locomotion,                         // kind: Ground | Bird, hop, speed, flee_speed
+    pub group: GroupKind,                               // Solitary | Group { leader: bool } | Flock
+    pub shelter: Shelter,                               // Burrow | Bush | Tree
+    pub routine: Routine,                               // Diurnal | Crepuscular | Nocturnal | MorningAfternoon
+    pub senses: Senses,                                 // vision, angle, hearing, smell, night_vision
+    pub needs: NeedRates,                               // hunger_per_h, thirst_per_h, fatigue_per_h, fear_threshold
+    pub health: HealthSpec,                             // max, pain_resist, heal_per_h, limp_below
+    pub personality: PersonalityBase,                   // base: BTreeMap&lt;Trait,u8&gt;, variation: BTreeMap&lt;Trait,u8&gt;
+    #[serde(default)] pub quirks: Vec&lt;String&gt;,
+    #[serde(default)] pub scent_marks: ScentMarks,      // enabled, kinds, meaning, every_min, lasts_h
+    pub brain: Brain,
+    pub activities: BTreeMap&lt;String, Activity&gt;,
+    #[serde(default)] pub animation_clips: BTreeMap&lt;String, String&gt;,
+}
+pub struct Brain { pub threat: ThreatBranch, pub choose: ChooseSpec }
+pub struct ThreatBranch { pub first: Vec&lt;(String, u8)&gt;, pub reactions: BTreeMap&lt;String, ReactionNode&gt; }
+pub struct ReactionNode { #[serde(rename = "do")] pub do_: Reaction, #[serde(default)] pub next: Vec&lt;(String, u8)&gt; }
+pub struct ChooseSpec { pub noise: f32, pub options: Vec&lt;String&gt; }
+pub type SpeciesId = String; /* a species' name, its key in the species table */ pub type NodeKey = String; pub type ActivityId = String; pub type WeightedRef = (NodeKey, u8); pub type SecsRange = (f32, f32);
+pub struct Activity { pub need: Need, pub curve: Curve, pub weight: f32, pub steps: Vec&lt;Step&gt; }
+pub struct Step { #[serde(rename = "do")] pub do_: StepKind, pub secs: (f32, f32), #[serde(default)] pub anim: Option&lt;String&gt; }</t>
+        </is>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -14422,7 +14503,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -15322,8 +15403,10 @@
       <c r="D45" s="4" t="s">
         <v>2279</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>2401</v>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hunger 95, rates 10, 20 game hours</t>
+        </is>
       </c>
       <c r="F45" s="4" t="s">
         <v>2402</v>
@@ -15682,8 +15765,10 @@
       <c r="E62" s="4" t="s">
         <v>2463</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>2464</v>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">same choice and scores, and other scores than with noise 0</t>
+        </is>
       </c>
       <c r="G62" s="4"/>
     </row>
@@ -15956,7 +16041,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">hunger 50, Eat step run long enough to take off 100</t>
+          <t xml:space="preserve">hunger half of what the whole Eat step takes off, the whole step run</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -15965,6 +16050,138 @@
         </is>
       </c>
       <c r="G73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-070</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-017</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rng::range</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">range(0, ∞), range(−MAX, MAX), range(0, NaN), range(NaN, 1)</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the lower end, no panic</t>
+        </is>
+      </c>
+      <c r="G74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-071</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-001</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tick</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dt −60, NaN, ∞</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">world unchanged</t>
+        </is>
+      </c>
+      <c r="G75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-072</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-011</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run_step</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hunger 50, Eat step with 3 s left run for 6 s</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hunger 8 (14 per s for 3 s)</t>
+        </is>
+      </c>
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT-073</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-010</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curve_eval</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x −0.2 on every curve</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0, never NaN</t>
+        </is>
+      </c>
+      <c r="G77" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16082,8 +16299,10 @@
       <c r="B10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>58</v>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brain graph editor: 26 API specifications</t>
+        </is>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16216,7 +16435,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">69 unit test cases (normal, boundary, abnormal)</t>
+          <t xml:space="preserve">73 unit test cases (normal, boundary, abnormal)</t>
         </is>
       </c>
     </row>
@@ -16314,8 +16533,10 @@
       <c r="A8" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>94</v>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALG-xx in sheet 5. Numbers are initial tuning values, each a named constant in the Config section of the file that uses it.</t>
+        </is>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
